--- a/CRM/wwwroot/files/clientes.xlsx
+++ b/CRM/wwwroot/files/clientes.xlsx
@@ -56,6 +56,3219 @@
   </x:si>
   <x:si>
     <x:t>DataProximoContato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13791</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07.359.218/0001-86</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TKR AUTO PECAS LTDA.ME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INATIVO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>corujatkr@hotmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11 36092511</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Alcides</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Osasco</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17/12/2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6877</x:t>
+  </x:si>
+  <x:si>
+    <x:t>60.926.714/0001-57</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARCEL DISTRIBUIDORA E COMERCIO DE AUTO PECAS LTDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATIVO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>marcelpecas@uol.com.br;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11 38583309</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rodrigo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SÃO PAULO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05/12/2025 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>583,26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>83494</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.499.963/0002-19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RV AUTO PECAS LTDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sara@rvautopecas.com.br</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11 42104600</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ricardo / Sara</x:t>
+  </x:si>
+  <x:si>
+    <x:t>São Paulo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19/11/2025 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3183,02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>94816</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19.275.708/0002-64</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TICO AUTO PECAS E DISTRIBUICAO LTDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>gerenciacompras@autopecastico.com.br</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11 48086670</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Adriano</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VARZEA PAULISTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13/11/2025 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2143,63</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15562</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01.170.181/0001-67</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PALMI CAR AUTO PECAS E ACESSORIOS LTDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>compras@palmicar.com.br</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11 941932438</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Daniele - Edilson</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Guarulhos</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12/12/2025 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>357,94</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20920</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.686.245/0001-78</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">IVAN DA ROCHA  </x:t>
+  </x:si>
+  <x:si>
+    <x:t>pecasnacional@hotmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14 996947647</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Viviane / Ivan</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bariri</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12/06/2025 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>354,24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>85620</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19.107.710/0001-43</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">CAETANO AUTO CENTER LTDA </x:t>
+  </x:si>
+  <x:si>
+    <x:t>contato@caetanoautocenter.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15 33055555</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Viviane</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tatuí</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20771</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.554.342/0001-20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDUARDO ARAUJO GARCIA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>garcia.automotive.vendas@hotmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18 996497580</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Eduardo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Clementina</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30/09/2025 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2388,38</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31454</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.245.158/0001-00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TATIANE ESTER TORRES AYMBIRE BERNEGOSSI 22595050826</x:t>
+  </x:si>
+  <x:si>
+    <x:t>antoniocarlosnevesbernegossi@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18 996816174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Antonio</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Penápolis</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29/07/2025 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>419,9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>45867</x:t>
+  </x:si>
+  <x:si>
+    <x:t>42.824.699/0002-35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BENVINDO PARAFUSOS LTDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>benvindoparafusos@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21 41012842</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Daniel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rio de Janeiro</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RJ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30054</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01.204.889/0003-53</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NAKUPENDA PECAS E SERVICOS LTDA ME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>compras.nakupenda@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21 968851197</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Max</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Teresópolis</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16901</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03.218.215/0001-71</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MORAESFRI COM.DE MAT.CONSTRUÇÃO LTDA.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>molaferchaveiro@hotmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22 25273031</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rogério</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NOVA FRIBURGO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22/10/2025 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3280,18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>32125</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.537.131/0001-99</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ITAFER COMERCIO LTDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>compras@cachoeiroparafusos.com.br;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28 999306246</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Juliano</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CACHOEIRO DO ITAPEMIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25289</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.698.755/0001-65</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REFRISUL COM. E SERV. DE REFRIGERAÇÃO LTDA EPP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>refrisul@live.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28 999811363</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Priscilla</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cachoeiro de Itapemirim</x:t>
+  </x:si>
+  <x:si>
+    <x:t>44435</x:t>
+  </x:si>
+  <x:si>
+    <x:t>32.631.895/0001-59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGF SUPER BOLTS COMERCIO DE FERRAGENS E FERRAMENTAS LTDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>vendas@agfsuperbolts.com.br</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31 33094202</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Marcelino</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Belo Horizonte</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1037,8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11901</x:t>
+  </x:si>
+  <x:si>
+    <x:t>00.847.347/0001-74</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SILVIO CEZAR FARIA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>silvio.faria21@yahoo.com.br</x:t>
+  </x:si>
+  <x:si>
+    <x:t>32 33451593</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Silvio</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTO RIO DOCE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31/10/2025 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1662,69</x:t>
+  </x:si>
+  <x:si>
+    <x:t>39216</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18.074.652/0001-36</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRANSBICO LTDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>autobico@hotmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>37 34214500</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sr Valdo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Luz</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18615</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.981.667/0001-92</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOTANIO MAQUINAS E IMPLEMENTOS AGRICOLAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>geraldosilvabarbosa@hotmail.com;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>37 35451131</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Vinicius </x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAINEIRAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29035</x:t>
+  </x:si>
+  <x:si>
+    <x:t>73.798.654/0001-86</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M DA COSTA PECAS ELETRICAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mar.san.1@hotmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43 999203471</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Marcelo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ribeirão do Pinhal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11/12/2025 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2228,83</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11340</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.683.157/0001-82</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JOAO MOTA DA SILVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>katiamota12@hotmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>81 988747971</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kátia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RECIFE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16339</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04.253.407/0001-81</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SHIGERU SHINOMIYA E CIA LTDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>orientalrolamentospa@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>91 991470833</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Higo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Castanhal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>47763</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.078.956/0001-22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>L FERNANDES DA SILVA LTDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>jlparafusocompras@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>99 984401961</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Luana</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Presidente Dutra</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14745</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08.455.820/0001-80</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AUTOBOR LTDA.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>autobor@hotmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>00 00000000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Geraldo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PATOS DE MINAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1257,2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>186</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07.330.701/0001-38</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AUTO PEÇAS OSCAMARGO LTDA.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>autopecascamargo@hotmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>João –  Marcelo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JOANOPOLIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10/12/2025 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2071,69</x:t>
+  </x:si>
+  <x:si>
+    <x:t>189</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01.939.321/0001-19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PARAFUSOS CAÇULA LTDA.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>p.cacula@hotmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Garcia / Éder</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CORUMBA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>276</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.956.346/0001-29</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AUTO PECAS GUANABARA LTDA.EPP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>autoguanabara@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Leomar</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANTA TERESA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5906</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01.303.599/0001-03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCB COMERCIO DE PARAFUSOS LTDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mcb.adm@buenoparafusos.com.br</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Marcos</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CAÇAPAVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25/09/2025 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2433,44</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6656</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01.876.765/0001-52</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RAIMUNDO CLAUDIO DE ALCANTARA LIMA ME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>papaiparafuso@yahoo.com.br</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Claudio/Valdemir</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FORTALEZA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05/09/2025 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1198,7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8394</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03.657.403/0001-04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POLO PARAFUSOS LTDA.EPP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>andrade_patriciaribeiro@hotmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Marco Polo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04/09/2025 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5820,52</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11699</x:t>
+  </x:si>
+  <x:si>
+    <x:t>63.422.570/0001-90</x:t>
+  </x:si>
+  <x:si>
+    <x:t>J.M.C. REIS ME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>josenildecr@gmail.com;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nádya</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAO LUIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12242</x:t>
+  </x:si>
+  <x:si>
+    <x:t>66.399.957/0001-60</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRENAUTO RETIFICA E LONAS LTDA.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>anelgo@hotmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Marcos / Godoi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UBERABA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3572,5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12649</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23.393.275/0001-38</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUMBERTO ESTEVAM DE SOUZA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>humbertoestevam2010@hotmail.com;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Humberto</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MALACACHETA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06/12/2024 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2153,06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13587</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.207.565/0001-68</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CASANOVA IND.E COM.TOLDOS ESQ.FERRO ALUMUNIO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>parafusosvistaalegre@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Marcus</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAO GONCALO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16/12/2025 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2210,7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13712</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.849.416/0001-00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FLORESTEC COMERCIO E SERVICOS EIRELI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>florestec_epi@hotmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Natanilza</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CAMANDUCAIA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08/10/2025 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>735,71</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15577</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01.350.827/0001-98</x:t>
+  </x:si>
+  <x:si>
+    <x:t>P. C. DOS SANTOS DISTRIBUIDORA AUTO PECAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rdezautopecas@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Paulo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRANCISCO MORATO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04/12/2025 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>373,13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16471</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04.985.559/0001-79</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRUST COMERCIAL LTDA.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>comprastrust@hotmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Vitor</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUARULHOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15/07/2025 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>746,75</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17766</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.827.722/0001-40</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CASA DO OLEO LTDA.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>casadooleocambui@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CAMBUI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05/06/2025 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>471,5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18106</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.330.904/0001-00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TOTTAL PARAFUSOS E PECAS LTDA.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tottalparafusos@yahoo.com.br</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ricardo – Marcos</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANANINDEUA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14/04/2025 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35439,66</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18720</x:t>
+  </x:si>
+  <x:si>
+    <x:t>86.589.496/0001-04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FLASH CAR LTDA.ME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rafael_msalgado@hotmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rafael</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MONTE SANTO DE MINAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19290</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.893.901/0001-76</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRUMAUTO COMERCIO DE AUTO PECAS LTDA.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>brumautocruzilia@hotmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Francisco</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRUZILIA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19419</x:t>
+  </x:si>
+  <x:si>
+    <x:t>76.076.199/0001-01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AUTO PECAS ANDORINHAS LTDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>autoandorinhas@hotmail.com;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Leandro</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARAPONGAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22/08/2025 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9252,04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20162</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.264.116/0001-42</x:t>
+  </x:si>
+  <x:si>
+    <x:t>J.F. DE SOUZA MARTINS ME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>avpneusdn@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>João Flávio</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DIVISA NOVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17/10/2025 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>951,39</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21331</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25.998.147/0001-43</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRAZCAR VEÍCULOS ESPECIAIS LTDA.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>almoxarifado@brazcar.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lindomar</x:t>
+  </x:si>
+  <x:si>
+    <x:t>677,8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21573</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18.697.025/0001-51</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A T PNEUS CENTRO AUTOMOTIVO LTDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>atpneus.centroautomotivo@hotmail.com;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Murilo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CAJATI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04/11/2025 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2623,25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22133</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04.674.688/0001-46</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEVANIR PINHEIRO LTDA.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>devanirpinheiro@uol.com.br</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Pinheiro</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RONDONOPOLIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27/06/2025 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2308,17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22267</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19.479.470/0001-08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F T FERNANDES FILHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>jlparafuso@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Damasio</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRESIDENTE DUTRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07.719.998/0001-28</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M. M. DE MORAES PECAS E SERVICOS ME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>paulista.pneus@bol.com.br</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Moises</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15/12/2025 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>393,38</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24122</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.395.663/0001-76</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PIOTO AUTO MEC.E COM. DE PEÇAS P/VEICULOS LTDA.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>osvaldopioto@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Pioto</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANTO ANDRE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13/06/2025 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>708,05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24379</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08.107.569/0001-62</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JOANNA DE MORAES ROCHA PARAFUSOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>compras2@polofix.com.br</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lucas / Joana / Jackson</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Salto de Pirapora</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29/09/2025 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1711,16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24548</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.249.832/0001-22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JUCESLINO &amp; FILHOS SERV.AUTOMOTIVOS LTDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>contato@continentalmec.com.br</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSASCO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24808</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.749.737/0001-03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GILSON RICCI DA SILVA FORMAROLO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>gspecasautomotivas@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Edmar / Gilson</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSVALDO CRUZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2027,21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26289</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29.862.627/0001-33</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PARAFUSOS CIA LTDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>parafusos.cia@hotmail.com;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02/12/2025 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1233,8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27808</x:t>
+  </x:si>
+  <x:si>
+    <x:t>33.953.392/0001-62</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARIO CHAMORRO 78490227187</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cicloparaiso@hotmail.com.br</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mario</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AQUIDAUANA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28071</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.064.832/0001-41</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JANAINA SANTOS MARTINS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>aemartins.adm@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Jonatas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOROCABA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28632</x:t>
+  </x:si>
+  <x:si>
+    <x:t>37.999.451/0001-94</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRITO PARAFUSOS EIRELI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>britoparafuso@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Naldo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Poa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30/06/2025 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1364,72</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28991</x:t>
+  </x:si>
+  <x:si>
+    <x:t>39.268.002/0001-00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LAGOS PARAFUSOS E FERRAMENTAS EIRELI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>vendas@lagosparafusoseferramentas.com.br;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MACAE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29491</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28.316.892/0001-53</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TIAGO DA SILVA FARIAS 35301876821</x:t>
+  </x:si>
+  <x:si>
+    <x:t>renato.opalaria@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Renato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29685</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.840.239/0001-96</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MC COMERCIO VAREJ.DE MATERIAL ELETRICO E FERRAGENS LTDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mv-medeiros@hotmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Medeiros</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANTA RITA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16/05/2025 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>787,2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31329</x:t>
+  </x:si>
+  <x:si>
+    <x:t>42.638.145/0001-62</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CACHOEIRO EPI S E FERRAMENTAS LTDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>a@b.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31340</x:t>
+  </x:si>
+  <x:si>
+    <x:t>34.752.161/0001-53</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LUCINEIDE DE SOUZA FERREIRA ALVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dasilvaferramentas01@gmail.com;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Da Silva</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PETROLINA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31595</x:t>
+  </x:si>
+  <x:si>
+    <x:t>42.824.699/0001-54</x:t>
+  </x:si>
+  <x:si>
+    <x:t>benvindoparafusos@gmail.com;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lucas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RIO DE JANEIRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31833</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43.597.691/0001-65</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FUSOMIX PARAFUSOS LTDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fusomixparafusos@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Thiago</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Palhoça</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18/08/2025 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1014,75</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31908</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.479.707/0001-30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RAQUEL KATIA DE OLIVEIRA SANTOS COM. DE PECAS AUT.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>vendas@calhasautomotivas.com.br;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Zeca</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAURU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31919</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.239.084/0001-25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COMERCIO VAREJISTA DE MATERIAIS DE CONSTRUÇÃO LS LTDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>netojacareba@hotmail.com;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Manoel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PORTO SEGURO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>32032</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.216.512/0001-76</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IENIS DE LIMA SCHMIDT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mauriciaschmidtgheno@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Vagner</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AMETISTA DO SUL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>32414</x:t>
+  </x:si>
+  <x:si>
+    <x:t>45.112.006/0001-99</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VALQUIRIA ALMEIDA SANTOS 05158526516</x:t>
+  </x:si>
+  <x:si>
+    <x:t>jrferramentasvc@gmail.com;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Valquiria</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOM JESUS DA SERRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>33750</x:t>
+  </x:si>
+  <x:si>
+    <x:t>39.639.723/0001-70</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROSANA DE SOUZA GALLEGO 11580053858</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mtbesportetotal@gmail.com;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>33756</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.740.353/0001-99</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TGM PECAS AUTOMOTIVA LTDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tgm.tgmautopecas@gmail.com;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Juan / Eduardo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>397,86</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35517</x:t>
+  </x:si>
+  <x:si>
+    <x:t>45.197.157/0001-97</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CENTRO AUTOMOTIVO STOPCAR LTDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>stopcarretocar@gmail.com;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Larissa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VARGINHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>36210</x:t>
+  </x:si>
+  <x:si>
+    <x:t>45.097.806/0001-88</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARCIA &amp; GARCIA IND E COM DE EQUIP.P/REPROD.DE AUDIO E VIDEO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>compras@tritonaltofalantes.com.br</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bruno</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Regente Feijo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>37853</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18.972.696/0001-83</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ST DA SILVA COMERCIO DE PECAS </x:t>
+  </x:si>
+  <x:si>
+    <x:t>stcomerciodepecas@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Daniela</x:t>
+  </x:si>
+  <x:si>
+    <x:t>38142</x:t>
+  </x:si>
+  <x:si>
+    <x:t>47.577.914/0001-83</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROBSON FERREIRA DA SILVA 54589827549</x:t>
+  </x:si>
+  <x:si>
+    <x:t>casasilvaveracruz@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Robson</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Vera Cruz</x:t>
+  </x:si>
+  <x:si>
+    <x:t>38397</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31.039.028/0001-66</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M. DA S. MENGUE &amp; V. A. DUARTE LTDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>casadosparafusoscapao@hotmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rodrigo / Morgana</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Capão Da Canoa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28/01/2025 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-1157,39</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10257</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04.497.756/0006-53</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A ALVES DE SOUSA INDUSTRIA E COMERCIO DE MOTOS LTDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sousatintas@hotmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rui</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Manaus</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28589</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29.410.949/0001-41</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NILCEA DA SILVA OLIVEIRA 07020843794</x:t>
+  </x:si>
+  <x:si>
+    <x:t>joaolenotintin@outlook.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>João?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sapucaia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26/11/2024 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2711,49</x:t>
+  </x:si>
+  <x:si>
+    <x:t>58392</x:t>
+  </x:si>
+  <x:si>
+    <x:t>57.441.991/0001-65</x:t>
+  </x:si>
+  <x:si>
+    <x:t>57.441.991 JOAO VITOR NUNES VIEIRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>gabriellenunes222@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gabrielle</x:t>
+  </x:si>
+  <x:si>
+    <x:t>São Vicente</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11/12/2024 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>505,84</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23130</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23.232.513/0001-23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUILHERME PERUCIO SOARES 00009629610</x:t>
+  </x:si>
+  <x:si>
+    <x:t>guilhermeperuciosoares@hotmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Guilherme</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tombos</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20/01/2025 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1300,25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20550</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.312.500/0001-36</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOUZA SELL COMERCIO DE AUTO PECAS LTDA.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sellautopecas@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dirlei</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Curitibanos</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31/07/2025 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5166,65</x:t>
+  </x:si>
+  <x:si>
+    <x:t>69154</x:t>
+  </x:si>
+  <x:si>
+    <x:t>57.084.008/0001-09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>57.084.008 JOAO PEDRO VIEIRA DE ABREU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>parautoptu@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>João Pedro</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Paracatu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25/08/2025 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>641</x:t>
+  </x:si>
+  <x:si>
+    <x:t>69864</x:t>
+  </x:si>
+  <x:si>
+    <x:t>59.719.297/0001-92</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IRMAOS SILVA VARIEDADES LTDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>vendas@aespecialistta.com.br</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Luciani</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ribeirão Preto</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23/09/2025 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>374,4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>73323</x:t>
+  </x:si>
+  <x:si>
+    <x:t>52.756.582/0001-34</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IMAEV IND DE MAQS E EQUIPAMENTOS VIBRATORIOS LTDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>compras@imaev.com.br</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dirce</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09/05/2025 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>375,2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>74342</x:t>
+  </x:si>
+  <x:si>
+    <x:t>60.917.765/0001-12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A P SILVA AUTO PECAS LTDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>alessandrodpaula78@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Alessandro / Eliseu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>São Sebastião do Anta</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1985,41</x:t>
+  </x:si>
+  <x:si>
+    <x:t>134</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.548.648/0001-68</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUARAPARI PARAFUSOS LTDA.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>guarapari.parafusos@bol.com.br</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cesar</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUARAPARI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23/10/2025 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1474,11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>403</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25.807.447/0001-06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ITAUNA PARAFUSOS LTDA.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>itaunaparafusos@gmail.com;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sr Iraci</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ITAUNA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12101</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.574.000/0001-20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NADISON PINTO DA LUZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mecanicacoligado@hotmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Coligado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EXTREMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12414</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03.049.750/0001-46</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAGE COMERCIO DE PECAS LTDA.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>reidosparafusos@oi.com.br;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Carlinhos</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MANHUACU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14/07/2025 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1107,38</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16324</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.238.114/0001-28</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNIFACIL AUTO PECAS MATIENSE EIRELI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>vendas-unifacil@hotmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MATIAS BARBOSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02/10/2025 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1219,69</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17533</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08.610.466/0001-10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GENIVALDO SOUZA SANTANA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>luanamonteirosilva2013@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Genivaldo Bisonho</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ITAPEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06/11/2025 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5004,31</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31099</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16.711.690/0001-27</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRITON INDUSTRIA E COMERCIO DE ALTO FALANTES LTDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>compras@tritonaltofalantes.com.br;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REGENTE FEIJO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1963,44</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4604</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.070.870/0001-20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUPERLATAS LTDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>superlatas@hotmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Célio</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UBERLANDIA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4055,42</x:t>
+  </x:si>
+  <x:si>
+    <x:t>32848</x:t>
+  </x:si>
+  <x:si>
+    <x:t>40.621.564/0001-66</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEDROSO PARAFUSOS COM DE FERRAGENS E FERRAMENTAS LTDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>lojapedrosoparafusos@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Marcelo Pedroso</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09/12/2025 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>647,81</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9195</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04.421.176/0001-78</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALADIM AUTO PECAS EIRELI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>luis@aladimautopecas.com.br;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Luis / Joice</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAO JOAO DA BOA VISTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07/11/2025 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2031,12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4354</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.637.988/0001-18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>J P SERRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>anavaleriaserra@hotmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Valéria</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Boa Vista</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3591,39</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5151</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01.034.738/0001-32</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AUTO MECANICA MARANI LTDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>compras@marani.com.br</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Roberto</x:t>
+  </x:si>
+  <x:si>
+    <x:t>611,83</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16268</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07.416.608/0001-40</x:t>
+  </x:si>
+  <x:si>
+    <x:t>J.R.G. DE MORAES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>guriborracharia@hotmail.com;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Janaina</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ITAPIRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3575,7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4170</x:t>
+  </x:si>
+  <x:si>
+    <x:t>38.967.626/0001-44</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AUTO PECAS PAGEVAR LTDA.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cris.pagevarpg@outlook.com;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Doka</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08/12/2025 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>559,13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15355</x:t>
+  </x:si>
+  <x:si>
+    <x:t>71.954.572/0001-58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AUTO PECAS PICOLO LTDA.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mapimino@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cesar / Marquinhos</x:t>
+  </x:si>
+  <x:si>
+    <x:t>471,12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16709</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07.264.702/0001-21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A J MARTINS FILHO PARAFUSOS E FERRAMENTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>multiparafuso@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18/11/2025 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>350,9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17134</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.217.926/0001-10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VIA RICA AUTO PECAS LTDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>viaricaautopecas@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Wallace - Anderson - Ricardo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mauá</x:t>
+  </x:si>
+  <x:si>
+    <x:t>527,66</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19842</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.112.027/0001-92</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CPG AUTO PECAS LTDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>poliparts01@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Pati</x:t>
+  </x:si>
+  <x:si>
+    <x:t>505,54</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23203</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01.069.520/0001-13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUPREMO COMERCIO DE AUTO PECAS LTDA ME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>pecassupremo@gmail.com;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Marcos / Dorival</x:t>
+  </x:si>
+  <x:si>
+    <x:t>378,32</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23875</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.155.399/0001-54</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M.R. SANTOS PECAS EPP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>comprasr10@globomail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Andre</x:t>
+  </x:si>
+  <x:si>
+    <x:t>956,62</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29375</x:t>
+  </x:si>
+  <x:si>
+    <x:t>39.153.818/0001-80</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ZAFRA COMERCIO DE PECAS LTDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>compras@zafraautopecas.com.br;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rafael / Henrique</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2736,9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27802</x:t>
+  </x:si>
+  <x:si>
+    <x:t>00.668.222/0001-87</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CTA DO BRASIL LTDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ctacompras2@cta-ultrasom.com.br</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Noelma</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Campanha</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11/06/2025 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>421,92</x:t>
+  </x:si>
+  <x:si>
+    <x:t>33248</x:t>
+  </x:si>
+  <x:si>
+    <x:t>32.279.252/0006-00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SCARIO PECAS AUTOMOTIVAS EIRELI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>filipebrito@scarioautopecas.com.br</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Filipe - Idelfonso</x:t>
+  </x:si>
+  <x:si>
+    <x:t>682,04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19093</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.332.064/0001-83</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANTONIO SIMÃO MENDES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>autobico@yahoo.com.br</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Evaldo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LUZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14/11/2025 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2237,84</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70608</x:t>
+  </x:si>
+  <x:si>
+    <x:t>51.375.568/0001-28</x:t>
+  </x:si>
+  <x:si>
+    <x:t>51.375.568 SUSANA COSTA DE JESUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>milipecas@hotmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Igor</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15390</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.444.829/0001-05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COFISA COML.FIXADORES SAPUCAIENSE LTDA.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cofisaparafusos@hotmail.com;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Paulo / Rafael</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAPUCAIA DO SUL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12/11/2025 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3085,24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17044</x:t>
+  </x:si>
+  <x:si>
+    <x:t>60.386.562/0001-47</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AUTO PEÇAS RATEIRO LTDA.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>compras@rateiro.com.br</x:t>
+  </x:si>
+  <x:si>
+    <x:t>585,3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21300</x:t>
+  </x:si>
+  <x:si>
+    <x:t>45.109.691/0006-09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>J.L. FURLAN E CIA. LTDA.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>speio@autopecasfurlan.com.br</x:t>
+  </x:si>
+  <x:si>
+    <x:t>André / Jefferson</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAO JOSE DO RIO PRETO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4446,21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21639</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.971.226/0001-93</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TATUI DIESEL COMERCIO DE PECAS E MANUT.DE VEIC.LTDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>vendas@tatuidiesel.com.br</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Neto</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TATUI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>906,69</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24478</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.006.001/0001-18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SATISFACTION AUTO PECAS LTDA.ME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>compras.satisfactionpecas@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Beto</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BARUERI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>730,19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18215</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07.340.393/0001-21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REY DOS PARAFUSOS LTDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>reydosparafusos@bol.com.br</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Giovane - Cleane</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Capão da Canoa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28/11/2025 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1334,06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17643</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.932.740/0001-10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>W.D. DE OLIVEIRA ME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>milrammoura@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06/01/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1540</x:t>
+  </x:si>
+  <x:si>
+    <x:t>59.517.763/0001-57</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LUIS DONISETE SAVIANI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>luissaviani@bol.com.br</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Luis</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAO SEBASTIAO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2524</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.959.693/0001-19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANTO INACIO AUTO PECAS LTDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>jpvmoreno@gmail.com;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>João</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3663</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.581.450/0001-22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UBERLATAS LTDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>uberlatasltda@yahoo.com.br</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Oberan</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16/07/2025 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2064,03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7823</x:t>
+  </x:si>
+  <x:si>
+    <x:t>71.675.615/0001-66</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TARGET INTERNATIONAL COMERCIO IMPORT. E EXPORT. LTDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>carlos.magno@targetinternational.com.br;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Carlos</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20/03/2025 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1275,12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15074</x:t>
+  </x:si>
+  <x:si>
+    <x:t>42.064.048/0001-03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOUZA COMERCIO VAREJISTA DE FERRAGEM LTDA.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>souza.comercio@hotmail.com;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Diego</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ILHEUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31/01/2025 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>840,76</x:t>
+  </x:si>
+  <x:si>
+    <x:t>32420</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08.395.306/0001-04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRIMUS IND E COM DE MAQ AGRICOLAS LTDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>luciano@maquinasprimus.com.br;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Luciano</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VENANCIO AIRES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20/10/2025 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7212</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>97.083.075/0001-15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AMAURI SCHMIDT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sulpecas03@hotmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>51 37183233</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Amauri / Diego</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VERA CRUZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6973,99</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07/01/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22653</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.318.285/0001-10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JOISAURO SANCHES DE OLIVEIRA JR 85354759315</x:t>
+  </x:si>
+  <x:si>
+    <x:t>j.junior.26@hotmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Junior / Thibério</x:t>
+  </x:si>
+  <x:si>
+    <x:t>São Luis</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7001,45</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9688</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.895.064/0001-30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MENDONCA E OLIVEIRA LTDA.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>jbmdeoliveira@uol.com.br</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Edson / Srº João</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOA VISTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10/10/2025 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5312,93</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10574</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08.704.203/0001-70</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARCEL DOS SANTOS DORNELES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>marcel_dorneles@hotmail.com;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Marcel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VIAMAO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03/12/2025 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5389,81</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17903</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.467.207/0001-94</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LUCIANA E. DE ARAÚJO PETROLINA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>casadosparafusos01@hotmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>835,4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30820</x:t>
+  </x:si>
+  <x:si>
+    <x:t>44.299.164/0001-37</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HELLWIG MATERIAIS DE CONSTRUCAO LTDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>megafixadores@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PELOTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24/11/2025 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1180,96</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31342</x:t>
+  </x:si>
+  <x:si>
+    <x:t>46.527.052/0001-11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JOSEVALDO ARAUJO DE QUEIROZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>casadosparafusos02@hotmail.com;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6014,21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5444</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01.204.889/0001-91</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NAKUPENDA PECAS E SERVICOS LTDA.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>maxisael84@outlook.com;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERESOPOLIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8626,07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12/01/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5972</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.315.951/0001-85</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M.S. KUMABE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>kumabetatui@hotmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cris / Dona Regina</x:t>
+  </x:si>
+  <x:si>
+    <x:t>694,65</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15251</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.883.404/0001-04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARCOS VINICIUS DE SOUZA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>marcosalinhauto@hotmail.com;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Marquinhos</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CAETE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1858,25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10084</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04.909.940/0001-59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RAMOS &amp; BERJAS JALES LTDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ripautopecas@hotmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ricardo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JALES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01/12/2025 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4374,97</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13869</x:t>
+  </x:si>
+  <x:si>
+    <x:t>52.331.477/0001-53</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A.C. RUIZ LTDA.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>marcoaurelio_cortez@hotmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Marco Aurélio</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRESIDENTE PRUDENTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13/01/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17914</x:t>
+  </x:si>
+  <x:si>
+    <x:t>69.973.337/0001-81</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FERGAMA PARAFUSOS LTDA.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fergamaparafusos@hotmail.com;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Oseas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MACEIO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1520,02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>77878</x:t>
+  </x:si>
+  <x:si>
+    <x:t>58.548.011/0001-90</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RV CASA DOS PARAFUSOS &amp; FERRAGENS LTDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>casadoparafuso1@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>81 36211482</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rosalice - Rafael</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Carpina</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13360,35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14/01/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13740</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.657.137/0001-37</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A. G. FIXADORES LTDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>marcelino@agfixadores.com.br</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2340</x:t>
+  </x:si>
+  <x:si>
+    <x:t>41.027.590/0001-23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IVAN MACHADO &amp; CIA. LTDA.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>prdaisymachado@hotmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Daisy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1141</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11/02/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8080</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.479.841/0001-06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CLEUDOMIRO F. SILVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>wnparafuso@hotmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>81 34421035</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cleodomiro</x:t>
+  </x:si>
+  <x:si>
+    <x:t>36998,27</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04/03/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26188</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.380.209/0005-21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACACIA  AUTO PEÇAS LTDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rsilva@acaciaauto.com.br</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Campinas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05/05/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6688</x:t>
+  </x:si>
+  <x:si>
+    <x:t>59.479.295/0001-73</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CARBWEL AUTO PECAS LTDA.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>compras@carbwel.com.br</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13301</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.023.691/0001-62</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NELTER DISTRIB.DE AUTO PECAS LTDA.ME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nelterautopecas@yahoo.com.br</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Felipe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31641</x:t>
+  </x:si>
+  <x:si>
+    <x:t>36.080.863/0001-63</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEUSDETE GONCALVES DOS SANTOS 00277743176</x:t>
+  </x:si>
+  <x:si>
+    <x:t>deusdetegonsalves51@gmail.com;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Deusdete</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NOVO SÃO JOAQUIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22322</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18.889.334/0001-23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HB 100 COMERCIO DE PECAS LTDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hb100sj@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Andrade</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05/07/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2410</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16.483.794/0001-21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FALCAO PARAFUSOS E FERRAGENS LTDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rodpar.parafusos@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FEIRA DE SANTANA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>658,9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19035</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.407.126/0001-07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAKAR PNEUS PECAS E SERVICOS LTDA.ME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tadeudakar@hotmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Luiz Tadeu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CASSIA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19/02/2025 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-236,1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03/10/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9274</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03.771.952/0001-05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JAIME PIVATTO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>jaimepivatto@hotmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ademir</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NOBRES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25636</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.546.355/0001-60</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROSINALDO SANTOS DE BRITO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>comerciodeparaf@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18/11/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>37390</x:t>
+  </x:si>
+  <x:si>
+    <x:t>51.660.903/0001-30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RADFIX DO NORTE LTDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>compras@radfixdonorte.com.br;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ITAÚBA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06/03/2025 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>598,8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.849.275/0001-18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>G M A COMERCIO DE PARAFUSOS EIRELI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>glauciomalves@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Glaucio</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03/12/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15860</x:t>
+  </x:si>
+  <x:si>
+    <x:t>compras.itaferbnh@gmail.com;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22692</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.076.080/0001-00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NEWCAR AUTO PECAS LTDA.ME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>newcarautopecas@hotmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Andson</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARABA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9983</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07.214.696/0001-06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M M S DISTRIBUIDORA AUTOMOTIVA LTDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>carlos@mmsautomotiva.com.br</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Eduardo / Juan</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03/12/2027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28969</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.499.963/0001-38</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ricardo@rvautopecas.com.br;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16/06/2025 00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2992,64</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04/08/2030</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -119,8 +3332,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:N2" totalsRowShown="0">
-  <x:autoFilter ref="A1:N2"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:N153" totalsRowShown="0">
+  <x:autoFilter ref="A1:N153"/>
   <x:tableColumns count="14">
     <x:tableColumn id="1" name="Codigo"/>
     <x:tableColumn id="2" name="Cnpj"/>
@@ -429,7 +3642,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:N2"/>
+  <x:dimension ref="A1:N153"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:14">
@@ -474,6 +3687,5464 @@
       </x:c>
       <x:c r="N1" s="0" t="s">
         <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:14">
+      <x:c r="A2" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C2" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D2" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E2" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F2" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G2" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H2" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I2" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="N2" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:14">
+      <x:c r="A3" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H3" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="I3" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J3" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="K3" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="N3" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:14">
+      <x:c r="A4" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="H4" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="I4" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J4" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="K4" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="N4" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:14">
+      <x:c r="A5" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="F5" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H5" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="I5" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J5" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="K5" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="N5" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:14">
+      <x:c r="A6" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="F6" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H6" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="I6" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J6" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="K6" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="N6" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:14">
+      <x:c r="A7" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="F7" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="G7" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="H7" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="I7" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J7" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="K7" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="N7" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:14">
+      <x:c r="A8" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="F8" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="G8" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="H8" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="I8" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="N8" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:14">
+      <x:c r="A9" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E9" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="F9" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="G9" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="H9" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="I9" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J9" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="K9" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="N9" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:14">
+      <x:c r="A10" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E10" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="F10" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="G10" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="H10" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="I10" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J10" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="K10" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="N10" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:14">
+      <x:c r="A11" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E11" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="F11" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="G11" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H11" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="I11" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="N11" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:14">
+      <x:c r="A12" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E12" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="F12" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="G12" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="H12" s="0" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="I12" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="N12" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:14">
+      <x:c r="A13" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="C13" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="D13" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E13" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="F13" s="0" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="G13" s="0" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="H13" s="0" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="I13" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="J13" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="K13" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="N13" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:14">
+      <x:c r="A14" s="0" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="C14" s="0" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="D14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E14" s="0" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="F14" s="0" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="G14" s="0" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="H14" s="0" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="I14" s="0" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="N14" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:14">
+      <x:c r="A15" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="B15" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="C15" s="0" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="D15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E15" s="0" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="F15" s="0" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="G15" s="0" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="H15" s="0" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="I15" s="0" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="N15" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:14">
+      <x:c r="A16" s="0" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="B16" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="C16" s="0" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="D16" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E16" s="0" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="F16" s="0" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="G16" s="0" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="H16" s="0" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="I16" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="J16" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="K16" s="0" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="N16" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:14">
+      <x:c r="A17" s="0" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="B17" s="0" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="C17" s="0" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="D17" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E17" s="0" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="F17" s="0" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="G17" s="0" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="H17" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="I17" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="J17" s="0" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="K17" s="0" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="N17" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:14">
+      <x:c r="A18" s="0" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="B18" s="0" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="C18" s="0" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="D18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E18" s="0" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="F18" s="0" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="G18" s="0" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="H18" s="0" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="I18" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="N18" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:14">
+      <x:c r="A19" s="0" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="B19" s="0" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="C19" s="0" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="D19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E19" s="0" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="F19" s="0" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G19" s="0" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="H19" s="0" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="I19" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="N19" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:14">
+      <x:c r="A20" s="0" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="B20" s="0" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="C20" s="0" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="D20" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E20" s="0" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="F20" s="0" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="G20" s="0" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="H20" s="0" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="I20" s="0" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="J20" s="0" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="K20" s="0" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="N20" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:14">
+      <x:c r="A21" s="0" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="B21" s="0" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="C21" s="0" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="D21" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E21" s="0" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="F21" s="0" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="G21" s="0" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="H21" s="0" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="I21" s="0" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="N21" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:14">
+      <x:c r="A22" s="0" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="B22" s="0" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="C22" s="0" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="D22" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E22" s="0" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="F22" s="0" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="G22" s="0" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="H22" s="0" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="I22" s="0" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="N22" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:14">
+      <x:c r="A23" s="0" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="B23" s="0" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="C23" s="0" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="D23" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E23" s="0" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="F23" s="0" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="G23" s="0" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="H23" s="0" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="I23" s="0" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="N23" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:14">
+      <x:c r="A24" s="0" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="B24" s="0" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="C24" s="0" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="D24" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E24" s="0" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="F24" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G24" s="0" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="H24" s="0" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="I24" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="J24" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="K24" s="0" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="N24" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:14">
+      <x:c r="A25" s="0" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="B25" s="0" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="C25" s="0" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="D25" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E25" s="0" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="F25" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G25" s="0" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="H25" s="0" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="I25" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J25" s="0" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="K25" s="0" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="N25" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:14">
+      <x:c r="A26" s="0" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="B26" s="0" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="C26" s="0" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="D26" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E26" s="0" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="F26" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G26" s="0" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="H26" s="0" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="I26" s="0" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="N26" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:14">
+      <x:c r="A27" s="0" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="B27" s="0" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="C27" s="0" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="D27" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E27" s="0" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="F27" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G27" s="0" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="H27" s="0" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="I27" s="0" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="N27" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:14">
+      <x:c r="A28" s="0" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="B28" s="0" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="C28" s="0" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="D28" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E28" s="0" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="F28" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G28" s="0" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="H28" s="0" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="I28" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J28" s="0" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="K28" s="0" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="N28" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:14">
+      <x:c r="A29" s="0" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="C29" s="0" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="D29" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E29" s="0" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="F29" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G29" s="0" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="H29" s="0" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="I29" s="0" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="J29" s="0" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="K29" s="0" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="N29" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:14">
+      <x:c r="A30" s="0" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="B30" s="0" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="C30" s="0" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="D30" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E30" s="0" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="F30" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G30" s="0" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="H30" s="0" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="I30" s="0" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="J30" s="0" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="K30" s="0" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="N30" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:14">
+      <x:c r="A31" s="0" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="B31" s="0" t="s">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="C31" s="0" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="D31" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E31" s="0" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F31" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G31" s="0" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="H31" s="0" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="I31" s="0" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="N31" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:14">
+      <x:c r="A32" s="0" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="B32" s="0" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="C32" s="0" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="D32" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E32" s="0" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="F32" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G32" s="0" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="H32" s="0" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="I32" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="J32" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="K32" s="0" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="N32" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:14">
+      <x:c r="A33" s="0" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="B33" s="0" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="C33" s="0" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="D33" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E33" s="0" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="F33" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G33" s="0" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="H33" s="0" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="I33" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="J33" s="0" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="K33" s="0" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="N33" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:14">
+      <x:c r="A34" s="0" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="B34" s="0" t="s">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="C34" s="0" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="D34" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E34" s="0" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="F34" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G34" s="0" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="H34" s="0" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="I34" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="J34" s="0" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="K34" s="0" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="N34" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:14">
+      <x:c r="A35" s="0" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="B35" s="0" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="C35" s="0" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="D35" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E35" s="0" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="F35" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G35" s="0" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="H35" s="0" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="I35" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="J35" s="0" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="K35" s="0" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="N35" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:14">
+      <x:c r="A36" s="0" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="B36" s="0" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="C36" s="0" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="D36" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E36" s="0" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="F36" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G36" s="0" t="s">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="H36" s="0" t="s">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="I36" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J36" s="0" t="s">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="K36" s="0" t="s">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="N36" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:14">
+      <x:c r="A37" s="0" t="s">
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="B37" s="0" t="s">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="C37" s="0" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="D37" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E37" s="0" t="s">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="F37" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G37" s="0" t="s">
+        <x:v>302</x:v>
+      </x:c>
+      <x:c r="H37" s="0" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="I37" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J37" s="0" t="s">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="K37" s="0" t="s">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="N37" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:14">
+      <x:c r="A38" s="0" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="B38" s="0" t="s">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="C38" s="0" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="D38" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E38" s="0" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="F38" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G38" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H38" s="0" t="s">
+        <x:v>310</x:v>
+      </x:c>
+      <x:c r="I38" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="J38" s="0" t="s">
+        <x:v>311</x:v>
+      </x:c>
+      <x:c r="K38" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="N38" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:14">
+      <x:c r="A39" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="B39" s="0" t="s">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="C39" s="0" t="s">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="D39" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E39" s="0" t="s">
+        <x:v>316</x:v>
+      </x:c>
+      <x:c r="F39" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G39" s="0" t="s">
+        <x:v>317</x:v>
+      </x:c>
+      <x:c r="H39" s="0" t="s">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="I39" s="0" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="J39" s="0" t="s">
+        <x:v>319</x:v>
+      </x:c>
+      <x:c r="K39" s="0" t="s">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="N39" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:14">
+      <x:c r="A40" s="0" t="s">
+        <x:v>321</x:v>
+      </x:c>
+      <x:c r="B40" s="0" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="C40" s="0" t="s">
+        <x:v>323</x:v>
+      </x:c>
+      <x:c r="D40" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E40" s="0" t="s">
+        <x:v>324</x:v>
+      </x:c>
+      <x:c r="F40" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G40" s="0" t="s">
+        <x:v>325</x:v>
+      </x:c>
+      <x:c r="H40" s="0" t="s">
+        <x:v>326</x:v>
+      </x:c>
+      <x:c r="I40" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="N40" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:14">
+      <x:c r="A41" s="0" t="s">
+        <x:v>327</x:v>
+      </x:c>
+      <x:c r="B41" s="0" t="s">
+        <x:v>328</x:v>
+      </x:c>
+      <x:c r="C41" s="0" t="s">
+        <x:v>329</x:v>
+      </x:c>
+      <x:c r="D41" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E41" s="0" t="s">
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="F41" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G41" s="0" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="H41" s="0" t="s">
+        <x:v>332</x:v>
+      </x:c>
+      <x:c r="I41" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="N41" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:14">
+      <x:c r="A42" s="0" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="B42" s="0" t="s">
+        <x:v>334</x:v>
+      </x:c>
+      <x:c r="C42" s="0" t="s">
+        <x:v>335</x:v>
+      </x:c>
+      <x:c r="D42" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E42" s="0" t="s">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="F42" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G42" s="0" t="s">
+        <x:v>337</x:v>
+      </x:c>
+      <x:c r="H42" s="0" t="s">
+        <x:v>338</x:v>
+      </x:c>
+      <x:c r="I42" s="0" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="J42" s="0" t="s">
+        <x:v>339</x:v>
+      </x:c>
+      <x:c r="K42" s="0" t="s">
+        <x:v>340</x:v>
+      </x:c>
+      <x:c r="N42" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:14">
+      <x:c r="A43" s="0" t="s">
+        <x:v>341</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
+        <x:v>342</x:v>
+      </x:c>
+      <x:c r="C43" s="0" t="s">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="D43" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E43" s="0" t="s">
+        <x:v>344</x:v>
+      </x:c>
+      <x:c r="F43" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G43" s="0" t="s">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="H43" s="0" t="s">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="I43" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="J43" s="0" t="s">
+        <x:v>347</x:v>
+      </x:c>
+      <x:c r="K43" s="0" t="s">
+        <x:v>348</x:v>
+      </x:c>
+      <x:c r="N43" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:14">
+      <x:c r="A44" s="0" t="s">
+        <x:v>349</x:v>
+      </x:c>
+      <x:c r="B44" s="0" t="s">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="C44" s="0" t="s">
+        <x:v>351</x:v>
+      </x:c>
+      <x:c r="D44" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E44" s="0" t="s">
+        <x:v>352</x:v>
+      </x:c>
+      <x:c r="F44" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G44" s="0" t="s">
+        <x:v>353</x:v>
+      </x:c>
+      <x:c r="H44" s="0" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="I44" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="J44" s="0" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="K44" s="0" t="s">
+        <x:v>354</x:v>
+      </x:c>
+      <x:c r="N44" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:14">
+      <x:c r="A45" s="0" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="B45" s="0" t="s">
+        <x:v>356</x:v>
+      </x:c>
+      <x:c r="C45" s="0" t="s">
+        <x:v>357</x:v>
+      </x:c>
+      <x:c r="D45" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E45" s="0" t="s">
+        <x:v>358</x:v>
+      </x:c>
+      <x:c r="F45" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G45" s="0" t="s">
+        <x:v>359</x:v>
+      </x:c>
+      <x:c r="H45" s="0" t="s">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="I45" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J45" s="0" t="s">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="K45" s="0" t="s">
+        <x:v>362</x:v>
+      </x:c>
+      <x:c r="N45" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:14">
+      <x:c r="A46" s="0" t="s">
+        <x:v>363</x:v>
+      </x:c>
+      <x:c r="B46" s="0" t="s">
+        <x:v>364</x:v>
+      </x:c>
+      <x:c r="C46" s="0" t="s">
+        <x:v>365</x:v>
+      </x:c>
+      <x:c r="D46" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E46" s="0" t="s">
+        <x:v>366</x:v>
+      </x:c>
+      <x:c r="F46" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G46" s="0" t="s">
+        <x:v>367</x:v>
+      </x:c>
+      <x:c r="H46" s="0" t="s">
+        <x:v>368</x:v>
+      </x:c>
+      <x:c r="I46" s="0" t="s">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="J46" s="0" t="s">
+        <x:v>370</x:v>
+      </x:c>
+      <x:c r="K46" s="0" t="s">
+        <x:v>371</x:v>
+      </x:c>
+      <x:c r="N46" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:14">
+      <x:c r="A47" s="0" t="s">
+        <x:v>372</x:v>
+      </x:c>
+      <x:c r="B47" s="0" t="s">
+        <x:v>373</x:v>
+      </x:c>
+      <x:c r="C47" s="0" t="s">
+        <x:v>374</x:v>
+      </x:c>
+      <x:c r="D47" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E47" s="0" t="s">
+        <x:v>375</x:v>
+      </x:c>
+      <x:c r="F47" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G47" s="0" t="s">
+        <x:v>376</x:v>
+      </x:c>
+      <x:c r="H47" s="0" t="s">
+        <x:v>377</x:v>
+      </x:c>
+      <x:c r="I47" s="0" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="N47" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:14">
+      <x:c r="A48" s="0" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="B48" s="0" t="s">
+        <x:v>379</x:v>
+      </x:c>
+      <x:c r="C48" s="0" t="s">
+        <x:v>380</x:v>
+      </x:c>
+      <x:c r="D48" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E48" s="0" t="s">
+        <x:v>381</x:v>
+      </x:c>
+      <x:c r="F48" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G48" s="0" t="s">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="H48" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="I48" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J48" s="0" t="s">
+        <x:v>383</x:v>
+      </x:c>
+      <x:c r="K48" s="0" t="s">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="N48" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:14">
+      <x:c r="A49" s="0" t="s">
+        <x:v>385</x:v>
+      </x:c>
+      <x:c r="B49" s="0" t="s">
+        <x:v>386</x:v>
+      </x:c>
+      <x:c r="C49" s="0" t="s">
+        <x:v>387</x:v>
+      </x:c>
+      <x:c r="D49" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E49" s="0" t="s">
+        <x:v>388</x:v>
+      </x:c>
+      <x:c r="F49" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G49" s="0" t="s">
+        <x:v>389</x:v>
+      </x:c>
+      <x:c r="H49" s="0" t="s">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="I49" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J49" s="0" t="s">
+        <x:v>391</x:v>
+      </x:c>
+      <x:c r="K49" s="0" t="s">
+        <x:v>392</x:v>
+      </x:c>
+      <x:c r="N49" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:14">
+      <x:c r="A50" s="0" t="s">
+        <x:v>393</x:v>
+      </x:c>
+      <x:c r="B50" s="0" t="s">
+        <x:v>394</x:v>
+      </x:c>
+      <x:c r="C50" s="0" t="s">
+        <x:v>395</x:v>
+      </x:c>
+      <x:c r="D50" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E50" s="0" t="s">
+        <x:v>396</x:v>
+      </x:c>
+      <x:c r="F50" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G50" s="0" t="s">
+        <x:v>397</x:v>
+      </x:c>
+      <x:c r="H50" s="0" t="s">
+        <x:v>398</x:v>
+      </x:c>
+      <x:c r="I50" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J50" s="0" t="s">
+        <x:v>399</x:v>
+      </x:c>
+      <x:c r="K50" s="0" t="s">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="N50" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:14">
+      <x:c r="A51" s="0" t="s">
+        <x:v>401</x:v>
+      </x:c>
+      <x:c r="B51" s="0" t="s">
+        <x:v>402</x:v>
+      </x:c>
+      <x:c r="C51" s="0" t="s">
+        <x:v>403</x:v>
+      </x:c>
+      <x:c r="D51" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E51" s="0" t="s">
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="F51" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G51" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H51" s="0" t="s">
+        <x:v>405</x:v>
+      </x:c>
+      <x:c r="I51" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="N51" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:14">
+      <x:c r="A52" s="0" t="s">
+        <x:v>406</x:v>
+      </x:c>
+      <x:c r="B52" s="0" t="s">
+        <x:v>407</x:v>
+      </x:c>
+      <x:c r="C52" s="0" t="s">
+        <x:v>408</x:v>
+      </x:c>
+      <x:c r="D52" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E52" s="0" t="s">
+        <x:v>409</x:v>
+      </x:c>
+      <x:c r="F52" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G52" s="0" t="s">
+        <x:v>410</x:v>
+      </x:c>
+      <x:c r="H52" s="0" t="s">
+        <x:v>411</x:v>
+      </x:c>
+      <x:c r="I52" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J52" s="0" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="K52" s="0" t="s">
+        <x:v>412</x:v>
+      </x:c>
+      <x:c r="N52" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:14">
+      <x:c r="A53" s="0" t="s">
+        <x:v>413</x:v>
+      </x:c>
+      <x:c r="B53" s="0" t="s">
+        <x:v>414</x:v>
+      </x:c>
+      <x:c r="C53" s="0" t="s">
+        <x:v>415</x:v>
+      </x:c>
+      <x:c r="D53" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E53" s="0" t="s">
+        <x:v>416</x:v>
+      </x:c>
+      <x:c r="F53" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G53" s="0" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="H53" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="I53" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J53" s="0" t="s">
+        <x:v>417</x:v>
+      </x:c>
+      <x:c r="K53" s="0" t="s">
+        <x:v>418</x:v>
+      </x:c>
+      <x:c r="N53" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:14">
+      <x:c r="A54" s="0" t="s">
+        <x:v>419</x:v>
+      </x:c>
+      <x:c r="B54" s="0" t="s">
+        <x:v>420</x:v>
+      </x:c>
+      <x:c r="C54" s="0" t="s">
+        <x:v>421</x:v>
+      </x:c>
+      <x:c r="D54" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E54" s="0" t="s">
+        <x:v>422</x:v>
+      </x:c>
+      <x:c r="F54" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G54" s="0" t="s">
+        <x:v>423</x:v>
+      </x:c>
+      <x:c r="H54" s="0" t="s">
+        <x:v>424</x:v>
+      </x:c>
+      <x:c r="I54" s="0" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="N54" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:14">
+      <x:c r="A55" s="0" t="s">
+        <x:v>425</x:v>
+      </x:c>
+      <x:c r="B55" s="0" t="s">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="C55" s="0" t="s">
+        <x:v>427</x:v>
+      </x:c>
+      <x:c r="D55" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E55" s="0" t="s">
+        <x:v>428</x:v>
+      </x:c>
+      <x:c r="F55" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G55" s="0" t="s">
+        <x:v>429</x:v>
+      </x:c>
+      <x:c r="H55" s="0" t="s">
+        <x:v>430</x:v>
+      </x:c>
+      <x:c r="I55" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="N55" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:14">
+      <x:c r="A56" s="0" t="s">
+        <x:v>431</x:v>
+      </x:c>
+      <x:c r="B56" s="0" t="s">
+        <x:v>432</x:v>
+      </x:c>
+      <x:c r="C56" s="0" t="s">
+        <x:v>433</x:v>
+      </x:c>
+      <x:c r="D56" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E56" s="0" t="s">
+        <x:v>434</x:v>
+      </x:c>
+      <x:c r="F56" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G56" s="0" t="s">
+        <x:v>435</x:v>
+      </x:c>
+      <x:c r="H56" s="0" t="s">
+        <x:v>436</x:v>
+      </x:c>
+      <x:c r="I56" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J56" s="0" t="s">
+        <x:v>437</x:v>
+      </x:c>
+      <x:c r="K56" s="0" t="s">
+        <x:v>438</x:v>
+      </x:c>
+      <x:c r="N56" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:14">
+      <x:c r="A57" s="0" t="s">
+        <x:v>439</x:v>
+      </x:c>
+      <x:c r="B57" s="0" t="s">
+        <x:v>440</x:v>
+      </x:c>
+      <x:c r="C57" s="0" t="s">
+        <x:v>441</x:v>
+      </x:c>
+      <x:c r="D57" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E57" s="0" t="s">
+        <x:v>442</x:v>
+      </x:c>
+      <x:c r="F57" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G57" s="0" t="s">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="H57" s="0" t="s">
+        <x:v>443</x:v>
+      </x:c>
+      <x:c r="I57" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="N57" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:14">
+      <x:c r="A58" s="0" t="s">
+        <x:v>444</x:v>
+      </x:c>
+      <x:c r="B58" s="0" t="s">
+        <x:v>445</x:v>
+      </x:c>
+      <x:c r="C58" s="0" t="s">
+        <x:v>446</x:v>
+      </x:c>
+      <x:c r="D58" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E58" s="0" t="s">
+        <x:v>447</x:v>
+      </x:c>
+      <x:c r="F58" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G58" s="0" t="s">
+        <x:v>448</x:v>
+      </x:c>
+      <x:c r="H58" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="I58" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="N58" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:14">
+      <x:c r="A59" s="0" t="s">
+        <x:v>449</x:v>
+      </x:c>
+      <x:c r="B59" s="0" t="s">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="C59" s="0" t="s">
+        <x:v>451</x:v>
+      </x:c>
+      <x:c r="D59" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E59" s="0" t="s">
+        <x:v>452</x:v>
+      </x:c>
+      <x:c r="F59" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G59" s="0" t="s">
+        <x:v>453</x:v>
+      </x:c>
+      <x:c r="H59" s="0" t="s">
+        <x:v>454</x:v>
+      </x:c>
+      <x:c r="I59" s="0" t="s">
+        <x:v>455</x:v>
+      </x:c>
+      <x:c r="J59" s="0" t="s">
+        <x:v>456</x:v>
+      </x:c>
+      <x:c r="K59" s="0" t="s">
+        <x:v>457</x:v>
+      </x:c>
+      <x:c r="N59" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:14">
+      <x:c r="A60" s="0" t="s">
+        <x:v>458</x:v>
+      </x:c>
+      <x:c r="B60" s="0" t="s">
+        <x:v>459</x:v>
+      </x:c>
+      <x:c r="C60" s="0" t="s">
+        <x:v>460</x:v>
+      </x:c>
+      <x:c r="D60" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E60" s="0" t="s">
+        <x:v>461</x:v>
+      </x:c>
+      <x:c r="F60" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G60" s="0" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="H60" s="0" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="I60" s="0" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="N60" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" spans="1:14">
+      <x:c r="A61" s="0" t="s">
+        <x:v>462</x:v>
+      </x:c>
+      <x:c r="B61" s="0" t="s">
+        <x:v>463</x:v>
+      </x:c>
+      <x:c r="C61" s="0" t="s">
+        <x:v>464</x:v>
+      </x:c>
+      <x:c r="D61" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E61" s="0" t="s">
+        <x:v>465</x:v>
+      </x:c>
+      <x:c r="F61" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G61" s="0" t="s">
+        <x:v>466</x:v>
+      </x:c>
+      <x:c r="H61" s="0" t="s">
+        <x:v>467</x:v>
+      </x:c>
+      <x:c r="I61" s="0" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="N61" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" spans="1:14">
+      <x:c r="A62" s="0" t="s">
+        <x:v>468</x:v>
+      </x:c>
+      <x:c r="B62" s="0" t="s">
+        <x:v>469</x:v>
+      </x:c>
+      <x:c r="C62" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="D62" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E62" s="0" t="s">
+        <x:v>470</x:v>
+      </x:c>
+      <x:c r="F62" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G62" s="0" t="s">
+        <x:v>471</x:v>
+      </x:c>
+      <x:c r="H62" s="0" t="s">
+        <x:v>472</x:v>
+      </x:c>
+      <x:c r="I62" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="N62" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" spans="1:14">
+      <x:c r="A63" s="0" t="s">
+        <x:v>473</x:v>
+      </x:c>
+      <x:c r="B63" s="0" t="s">
+        <x:v>474</x:v>
+      </x:c>
+      <x:c r="C63" s="0" t="s">
+        <x:v>475</x:v>
+      </x:c>
+      <x:c r="D63" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E63" s="0" t="s">
+        <x:v>476</x:v>
+      </x:c>
+      <x:c r="F63" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G63" s="0" t="s">
+        <x:v>477</x:v>
+      </x:c>
+      <x:c r="H63" s="0" t="s">
+        <x:v>478</x:v>
+      </x:c>
+      <x:c r="I63" s="0" t="s">
+        <x:v>479</x:v>
+      </x:c>
+      <x:c r="J63" s="0" t="s">
+        <x:v>480</x:v>
+      </x:c>
+      <x:c r="K63" s="0" t="s">
+        <x:v>481</x:v>
+      </x:c>
+      <x:c r="N63" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" spans="1:14">
+      <x:c r="A64" s="0" t="s">
+        <x:v>482</x:v>
+      </x:c>
+      <x:c r="B64" s="0" t="s">
+        <x:v>483</x:v>
+      </x:c>
+      <x:c r="C64" s="0" t="s">
+        <x:v>484</x:v>
+      </x:c>
+      <x:c r="D64" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E64" s="0" t="s">
+        <x:v>485</x:v>
+      </x:c>
+      <x:c r="F64" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G64" s="0" t="s">
+        <x:v>486</x:v>
+      </x:c>
+      <x:c r="H64" s="0" t="s">
+        <x:v>487</x:v>
+      </x:c>
+      <x:c r="I64" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="N64" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" spans="1:14">
+      <x:c r="A65" s="0" t="s">
+        <x:v>488</x:v>
+      </x:c>
+      <x:c r="B65" s="0" t="s">
+        <x:v>489</x:v>
+      </x:c>
+      <x:c r="C65" s="0" t="s">
+        <x:v>490</x:v>
+      </x:c>
+      <x:c r="D65" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E65" s="0" t="s">
+        <x:v>491</x:v>
+      </x:c>
+      <x:c r="F65" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G65" s="0" t="s">
+        <x:v>492</x:v>
+      </x:c>
+      <x:c r="H65" s="0" t="s">
+        <x:v>493</x:v>
+      </x:c>
+      <x:c r="I65" s="0" t="s">
+        <x:v>494</x:v>
+      </x:c>
+      <x:c r="N65" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" spans="1:14">
+      <x:c r="A66" s="0" t="s">
+        <x:v>495</x:v>
+      </x:c>
+      <x:c r="B66" s="0" t="s">
+        <x:v>496</x:v>
+      </x:c>
+      <x:c r="C66" s="0" t="s">
+        <x:v>497</x:v>
+      </x:c>
+      <x:c r="D66" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E66" s="0" t="s">
+        <x:v>498</x:v>
+      </x:c>
+      <x:c r="F66" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G66" s="0" t="s">
+        <x:v>499</x:v>
+      </x:c>
+      <x:c r="H66" s="0" t="s">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="I66" s="0" t="s">
+        <x:v>501</x:v>
+      </x:c>
+      <x:c r="N66" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" spans="1:14">
+      <x:c r="A67" s="0" t="s">
+        <x:v>502</x:v>
+      </x:c>
+      <x:c r="B67" s="0" t="s">
+        <x:v>503</x:v>
+      </x:c>
+      <x:c r="C67" s="0" t="s">
+        <x:v>504</x:v>
+      </x:c>
+      <x:c r="D67" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E67" s="0" t="s">
+        <x:v>505</x:v>
+      </x:c>
+      <x:c r="F67" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G67" s="0" t="s">
+        <x:v>506</x:v>
+      </x:c>
+      <x:c r="H67" s="0" t="s">
+        <x:v>507</x:v>
+      </x:c>
+      <x:c r="I67" s="0" t="s">
+        <x:v>494</x:v>
+      </x:c>
+      <x:c r="N67" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" spans="1:14">
+      <x:c r="A68" s="0" t="s">
+        <x:v>508</x:v>
+      </x:c>
+      <x:c r="B68" s="0" t="s">
+        <x:v>509</x:v>
+      </x:c>
+      <x:c r="C68" s="0" t="s">
+        <x:v>510</x:v>
+      </x:c>
+      <x:c r="D68" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E68" s="0" t="s">
+        <x:v>511</x:v>
+      </x:c>
+      <x:c r="F68" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G68" s="0" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="H68" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="I68" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="N68" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" spans="1:14">
+      <x:c r="A69" s="0" t="s">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="B69" s="0" t="s">
+        <x:v>513</x:v>
+      </x:c>
+      <x:c r="C69" s="0" t="s">
+        <x:v>514</x:v>
+      </x:c>
+      <x:c r="D69" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E69" s="0" t="s">
+        <x:v>515</x:v>
+      </x:c>
+      <x:c r="F69" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G69" s="0" t="s">
+        <x:v>516</x:v>
+      </x:c>
+      <x:c r="H69" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="I69" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J69" s="0" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="K69" s="0" t="s">
+        <x:v>517</x:v>
+      </x:c>
+      <x:c r="N69" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" spans="1:14">
+      <x:c r="A70" s="0" t="s">
+        <x:v>518</x:v>
+      </x:c>
+      <x:c r="B70" s="0" t="s">
+        <x:v>519</x:v>
+      </x:c>
+      <x:c r="C70" s="0" t="s">
+        <x:v>520</x:v>
+      </x:c>
+      <x:c r="D70" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E70" s="0" t="s">
+        <x:v>521</x:v>
+      </x:c>
+      <x:c r="F70" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G70" s="0" t="s">
+        <x:v>522</x:v>
+      </x:c>
+      <x:c r="H70" s="0" t="s">
+        <x:v>523</x:v>
+      </x:c>
+      <x:c r="I70" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="N70" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" spans="1:14">
+      <x:c r="A71" s="0" t="s">
+        <x:v>524</x:v>
+      </x:c>
+      <x:c r="B71" s="0" t="s">
+        <x:v>525</x:v>
+      </x:c>
+      <x:c r="C71" s="0" t="s">
+        <x:v>526</x:v>
+      </x:c>
+      <x:c r="D71" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E71" s="0" t="s">
+        <x:v>527</x:v>
+      </x:c>
+      <x:c r="F71" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G71" s="0" t="s">
+        <x:v>528</x:v>
+      </x:c>
+      <x:c r="H71" s="0" t="s">
+        <x:v>529</x:v>
+      </x:c>
+      <x:c r="I71" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="N71" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" spans="1:14">
+      <x:c r="A72" s="0" t="s">
+        <x:v>530</x:v>
+      </x:c>
+      <x:c r="B72" s="0" t="s">
+        <x:v>531</x:v>
+      </x:c>
+      <x:c r="C72" s="0" t="s">
+        <x:v>532</x:v>
+      </x:c>
+      <x:c r="D72" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E72" s="0" t="s">
+        <x:v>533</x:v>
+      </x:c>
+      <x:c r="F72" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G72" s="0" t="s">
+        <x:v>534</x:v>
+      </x:c>
+      <x:c r="H72" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="I72" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="N72" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" spans="1:14">
+      <x:c r="A73" s="0" t="s">
+        <x:v>535</x:v>
+      </x:c>
+      <x:c r="B73" s="0" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="C73" s="0" t="s">
+        <x:v>537</x:v>
+      </x:c>
+      <x:c r="D73" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E73" s="0" t="s">
+        <x:v>538</x:v>
+      </x:c>
+      <x:c r="F73" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G73" s="0" t="s">
+        <x:v>539</x:v>
+      </x:c>
+      <x:c r="H73" s="0" t="s">
+        <x:v>540</x:v>
+      </x:c>
+      <x:c r="I73" s="0" t="s">
+        <x:v>494</x:v>
+      </x:c>
+      <x:c r="N73" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" spans="1:14">
+      <x:c r="A74" s="0" t="s">
+        <x:v>541</x:v>
+      </x:c>
+      <x:c r="B74" s="0" t="s">
+        <x:v>542</x:v>
+      </x:c>
+      <x:c r="C74" s="0" t="s">
+        <x:v>543</x:v>
+      </x:c>
+      <x:c r="D74" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E74" s="0" t="s">
+        <x:v>544</x:v>
+      </x:c>
+      <x:c r="F74" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G74" s="0" t="s">
+        <x:v>545</x:v>
+      </x:c>
+      <x:c r="H74" s="0" t="s">
+        <x:v>546</x:v>
+      </x:c>
+      <x:c r="I74" s="0" t="s">
+        <x:v>501</x:v>
+      </x:c>
+      <x:c r="J74" s="0" t="s">
+        <x:v>547</x:v>
+      </x:c>
+      <x:c r="K74" s="0" t="s">
+        <x:v>548</x:v>
+      </x:c>
+      <x:c r="N74" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" spans="1:14">
+      <x:c r="A75" s="0" t="s">
+        <x:v>549</x:v>
+      </x:c>
+      <x:c r="B75" s="0" t="s">
+        <x:v>550</x:v>
+      </x:c>
+      <x:c r="C75" s="0" t="s">
+        <x:v>551</x:v>
+      </x:c>
+      <x:c r="D75" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E75" s="0" t="s">
+        <x:v>552</x:v>
+      </x:c>
+      <x:c r="F75" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G75" s="0" t="s">
+        <x:v>553</x:v>
+      </x:c>
+      <x:c r="H75" s="0" t="s">
+        <x:v>554</x:v>
+      </x:c>
+      <x:c r="I75" s="0" t="s">
+        <x:v>555</x:v>
+      </x:c>
+      <x:c r="N75" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" spans="1:14">
+      <x:c r="A76" s="0" t="s">
+        <x:v>556</x:v>
+      </x:c>
+      <x:c r="B76" s="0" t="s">
+        <x:v>557</x:v>
+      </x:c>
+      <x:c r="C76" s="0" t="s">
+        <x:v>558</x:v>
+      </x:c>
+      <x:c r="D76" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E76" s="0" t="s">
+        <x:v>559</x:v>
+      </x:c>
+      <x:c r="F76" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G76" s="0" t="s">
+        <x:v>560</x:v>
+      </x:c>
+      <x:c r="H76" s="0" t="s">
+        <x:v>561</x:v>
+      </x:c>
+      <x:c r="I76" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="J76" s="0" t="s">
+        <x:v>562</x:v>
+      </x:c>
+      <x:c r="K76" s="0" t="s">
+        <x:v>563</x:v>
+      </x:c>
+      <x:c r="N76" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" spans="1:14">
+      <x:c r="A77" s="0" t="s">
+        <x:v>564</x:v>
+      </x:c>
+      <x:c r="B77" s="0" t="s">
+        <x:v>565</x:v>
+      </x:c>
+      <x:c r="C77" s="0" t="s">
+        <x:v>566</x:v>
+      </x:c>
+      <x:c r="D77" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E77" s="0" t="s">
+        <x:v>567</x:v>
+      </x:c>
+      <x:c r="F77" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G77" s="0" t="s">
+        <x:v>568</x:v>
+      </x:c>
+      <x:c r="H77" s="0" t="s">
+        <x:v>569</x:v>
+      </x:c>
+      <x:c r="I77" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J77" s="0" t="s">
+        <x:v>570</x:v>
+      </x:c>
+      <x:c r="K77" s="0" t="s">
+        <x:v>571</x:v>
+      </x:c>
+      <x:c r="N77" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" spans="1:14">
+      <x:c r="A78" s="0" t="s">
+        <x:v>572</x:v>
+      </x:c>
+      <x:c r="B78" s="0" t="s">
+        <x:v>573</x:v>
+      </x:c>
+      <x:c r="C78" s="0" t="s">
+        <x:v>574</x:v>
+      </x:c>
+      <x:c r="D78" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E78" s="0" t="s">
+        <x:v>575</x:v>
+      </x:c>
+      <x:c r="F78" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G78" s="0" t="s">
+        <x:v>576</x:v>
+      </x:c>
+      <x:c r="H78" s="0" t="s">
+        <x:v>577</x:v>
+      </x:c>
+      <x:c r="I78" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="J78" s="0" t="s">
+        <x:v>578</x:v>
+      </x:c>
+      <x:c r="K78" s="0" t="s">
+        <x:v>579</x:v>
+      </x:c>
+      <x:c r="N78" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" spans="1:14">
+      <x:c r="A79" s="0" t="s">
+        <x:v>580</x:v>
+      </x:c>
+      <x:c r="B79" s="0" t="s">
+        <x:v>581</x:v>
+      </x:c>
+      <x:c r="C79" s="0" t="s">
+        <x:v>582</x:v>
+      </x:c>
+      <x:c r="D79" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E79" s="0" t="s">
+        <x:v>583</x:v>
+      </x:c>
+      <x:c r="F79" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G79" s="0" t="s">
+        <x:v>584</x:v>
+      </x:c>
+      <x:c r="H79" s="0" t="s">
+        <x:v>585</x:v>
+      </x:c>
+      <x:c r="I79" s="0" t="s">
+        <x:v>479</x:v>
+      </x:c>
+      <x:c r="J79" s="0" t="s">
+        <x:v>586</x:v>
+      </x:c>
+      <x:c r="K79" s="0" t="s">
+        <x:v>587</x:v>
+      </x:c>
+      <x:c r="N79" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" spans="1:14">
+      <x:c r="A80" s="0" t="s">
+        <x:v>588</x:v>
+      </x:c>
+      <x:c r="B80" s="0" t="s">
+        <x:v>589</x:v>
+      </x:c>
+      <x:c r="C80" s="0" t="s">
+        <x:v>590</x:v>
+      </x:c>
+      <x:c r="D80" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E80" s="0" t="s">
+        <x:v>591</x:v>
+      </x:c>
+      <x:c r="F80" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G80" s="0" t="s">
+        <x:v>592</x:v>
+      </x:c>
+      <x:c r="H80" s="0" t="s">
+        <x:v>593</x:v>
+      </x:c>
+      <x:c r="I80" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="J80" s="0" t="s">
+        <x:v>594</x:v>
+      </x:c>
+      <x:c r="K80" s="0" t="s">
+        <x:v>595</x:v>
+      </x:c>
+      <x:c r="N80" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" spans="1:14">
+      <x:c r="A81" s="0" t="s">
+        <x:v>596</x:v>
+      </x:c>
+      <x:c r="B81" s="0" t="s">
+        <x:v>597</x:v>
+      </x:c>
+      <x:c r="C81" s="0" t="s">
+        <x:v>598</x:v>
+      </x:c>
+      <x:c r="D81" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E81" s="0" t="s">
+        <x:v>599</x:v>
+      </x:c>
+      <x:c r="F81" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G81" s="0" t="s">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="H81" s="0" t="s">
+        <x:v>601</x:v>
+      </x:c>
+      <x:c r="I81" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J81" s="0" t="s">
+        <x:v>602</x:v>
+      </x:c>
+      <x:c r="K81" s="0" t="s">
+        <x:v>603</x:v>
+      </x:c>
+      <x:c r="N81" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" spans="1:14">
+      <x:c r="A82" s="0" t="s">
+        <x:v>604</x:v>
+      </x:c>
+      <x:c r="B82" s="0" t="s">
+        <x:v>605</x:v>
+      </x:c>
+      <x:c r="C82" s="0" t="s">
+        <x:v>606</x:v>
+      </x:c>
+      <x:c r="D82" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E82" s="0" t="s">
+        <x:v>607</x:v>
+      </x:c>
+      <x:c r="F82" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G82" s="0" t="s">
+        <x:v>608</x:v>
+      </x:c>
+      <x:c r="H82" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I82" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J82" s="0" t="s">
+        <x:v>609</x:v>
+      </x:c>
+      <x:c r="K82" s="0" t="s">
+        <x:v>610</x:v>
+      </x:c>
+      <x:c r="N82" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" spans="1:14">
+      <x:c r="A83" s="0" t="s">
+        <x:v>611</x:v>
+      </x:c>
+      <x:c r="B83" s="0" t="s">
+        <x:v>612</x:v>
+      </x:c>
+      <x:c r="C83" s="0" t="s">
+        <x:v>613</x:v>
+      </x:c>
+      <x:c r="D83" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E83" s="0" t="s">
+        <x:v>614</x:v>
+      </x:c>
+      <x:c r="F83" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G83" s="0" t="s">
+        <x:v>615</x:v>
+      </x:c>
+      <x:c r="H83" s="0" t="s">
+        <x:v>616</x:v>
+      </x:c>
+      <x:c r="I83" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="J83" s="0" t="s">
+        <x:v>370</x:v>
+      </x:c>
+      <x:c r="K83" s="0" t="s">
+        <x:v>617</x:v>
+      </x:c>
+      <x:c r="N83" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" spans="1:14">
+      <x:c r="A84" s="0" t="s">
+        <x:v>618</x:v>
+      </x:c>
+      <x:c r="B84" s="0" t="s">
+        <x:v>619</x:v>
+      </x:c>
+      <x:c r="C84" s="0" t="s">
+        <x:v>620</x:v>
+      </x:c>
+      <x:c r="D84" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E84" s="0" t="s">
+        <x:v>621</x:v>
+      </x:c>
+      <x:c r="F84" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G84" s="0" t="s">
+        <x:v>622</x:v>
+      </x:c>
+      <x:c r="H84" s="0" t="s">
+        <x:v>623</x:v>
+      </x:c>
+      <x:c r="I84" s="0" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="J84" s="0" t="s">
+        <x:v>624</x:v>
+      </x:c>
+      <x:c r="K84" s="0" t="s">
+        <x:v>625</x:v>
+      </x:c>
+      <x:c r="N84" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" spans="1:14">
+      <x:c r="A85" s="0" t="s">
+        <x:v>626</x:v>
+      </x:c>
+      <x:c r="B85" s="0" t="s">
+        <x:v>627</x:v>
+      </x:c>
+      <x:c r="C85" s="0" t="s">
+        <x:v>628</x:v>
+      </x:c>
+      <x:c r="D85" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E85" s="0" t="s">
+        <x:v>629</x:v>
+      </x:c>
+      <x:c r="F85" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G85" s="0" t="s">
+        <x:v>630</x:v>
+      </x:c>
+      <x:c r="H85" s="0" t="s">
+        <x:v>631</x:v>
+      </x:c>
+      <x:c r="I85" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="N85" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" spans="1:14">
+      <x:c r="A86" s="0" t="s">
+        <x:v>632</x:v>
+      </x:c>
+      <x:c r="B86" s="0" t="s">
+        <x:v>633</x:v>
+      </x:c>
+      <x:c r="C86" s="0" t="s">
+        <x:v>634</x:v>
+      </x:c>
+      <x:c r="D86" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E86" s="0" t="s">
+        <x:v>635</x:v>
+      </x:c>
+      <x:c r="F86" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G86" s="0" t="s">
+        <x:v>636</x:v>
+      </x:c>
+      <x:c r="H86" s="0" t="s">
+        <x:v>637</x:v>
+      </x:c>
+      <x:c r="I86" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="N86" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" spans="1:14">
+      <x:c r="A87" s="0" t="s">
+        <x:v>638</x:v>
+      </x:c>
+      <x:c r="B87" s="0" t="s">
+        <x:v>639</x:v>
+      </x:c>
+      <x:c r="C87" s="0" t="s">
+        <x:v>640</x:v>
+      </x:c>
+      <x:c r="D87" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E87" s="0" t="s">
+        <x:v>641</x:v>
+      </x:c>
+      <x:c r="F87" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G87" s="0" t="s">
+        <x:v>642</x:v>
+      </x:c>
+      <x:c r="H87" s="0" t="s">
+        <x:v>643</x:v>
+      </x:c>
+      <x:c r="I87" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="J87" s="0" t="s">
+        <x:v>644</x:v>
+      </x:c>
+      <x:c r="K87" s="0" t="s">
+        <x:v>645</x:v>
+      </x:c>
+      <x:c r="N87" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" spans="1:14">
+      <x:c r="A88" s="0" t="s">
+        <x:v>646</x:v>
+      </x:c>
+      <x:c r="B88" s="0" t="s">
+        <x:v>647</x:v>
+      </x:c>
+      <x:c r="C88" s="0" t="s">
+        <x:v>648</x:v>
+      </x:c>
+      <x:c r="D88" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E88" s="0" t="s">
+        <x:v>649</x:v>
+      </x:c>
+      <x:c r="F88" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G88" s="0" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="H88" s="0" t="s">
+        <x:v>650</x:v>
+      </x:c>
+      <x:c r="I88" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="J88" s="0" t="s">
+        <x:v>651</x:v>
+      </x:c>
+      <x:c r="K88" s="0" t="s">
+        <x:v>652</x:v>
+      </x:c>
+      <x:c r="N88" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" spans="1:14">
+      <x:c r="A89" s="0" t="s">
+        <x:v>653</x:v>
+      </x:c>
+      <x:c r="B89" s="0" t="s">
+        <x:v>654</x:v>
+      </x:c>
+      <x:c r="C89" s="0" t="s">
+        <x:v>655</x:v>
+      </x:c>
+      <x:c r="D89" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E89" s="0" t="s">
+        <x:v>656</x:v>
+      </x:c>
+      <x:c r="F89" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G89" s="0" t="s">
+        <x:v>657</x:v>
+      </x:c>
+      <x:c r="H89" s="0" t="s">
+        <x:v>658</x:v>
+      </x:c>
+      <x:c r="I89" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="J89" s="0" t="s">
+        <x:v>659</x:v>
+      </x:c>
+      <x:c r="K89" s="0" t="s">
+        <x:v>660</x:v>
+      </x:c>
+      <x:c r="N89" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" spans="1:14">
+      <x:c r="A90" s="0" t="s">
+        <x:v>661</x:v>
+      </x:c>
+      <x:c r="B90" s="0" t="s">
+        <x:v>662</x:v>
+      </x:c>
+      <x:c r="C90" s="0" t="s">
+        <x:v>663</x:v>
+      </x:c>
+      <x:c r="D90" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E90" s="0" t="s">
+        <x:v>664</x:v>
+      </x:c>
+      <x:c r="F90" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G90" s="0" t="s">
+        <x:v>423</x:v>
+      </x:c>
+      <x:c r="H90" s="0" t="s">
+        <x:v>665</x:v>
+      </x:c>
+      <x:c r="I90" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J90" s="0" t="s">
+        <x:v>383</x:v>
+      </x:c>
+      <x:c r="K90" s="0" t="s">
+        <x:v>666</x:v>
+      </x:c>
+      <x:c r="N90" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" spans="1:14">
+      <x:c r="A91" s="0" t="s">
+        <x:v>667</x:v>
+      </x:c>
+      <x:c r="B91" s="0" t="s">
+        <x:v>668</x:v>
+      </x:c>
+      <x:c r="C91" s="0" t="s">
+        <x:v>669</x:v>
+      </x:c>
+      <x:c r="D91" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E91" s="0" t="s">
+        <x:v>670</x:v>
+      </x:c>
+      <x:c r="F91" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G91" s="0" t="s">
+        <x:v>671</x:v>
+      </x:c>
+      <x:c r="H91" s="0" t="s">
+        <x:v>672</x:v>
+      </x:c>
+      <x:c r="I91" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="J91" s="0" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="K91" s="0" t="s">
+        <x:v>673</x:v>
+      </x:c>
+      <x:c r="N91" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" spans="1:14">
+      <x:c r="A92" s="0" t="s">
+        <x:v>674</x:v>
+      </x:c>
+      <x:c r="B92" s="0" t="s">
+        <x:v>675</x:v>
+      </x:c>
+      <x:c r="C92" s="0" t="s">
+        <x:v>676</x:v>
+      </x:c>
+      <x:c r="D92" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E92" s="0" t="s">
+        <x:v>677</x:v>
+      </x:c>
+      <x:c r="F92" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G92" s="0" t="s">
+        <x:v>678</x:v>
+      </x:c>
+      <x:c r="H92" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I92" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J92" s="0" t="s">
+        <x:v>679</x:v>
+      </x:c>
+      <x:c r="K92" s="0" t="s">
+        <x:v>680</x:v>
+      </x:c>
+      <x:c r="N92" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" spans="1:14">
+      <x:c r="A93" s="0" t="s">
+        <x:v>681</x:v>
+      </x:c>
+      <x:c r="B93" s="0" t="s">
+        <x:v>682</x:v>
+      </x:c>
+      <x:c r="C93" s="0" t="s">
+        <x:v>683</x:v>
+      </x:c>
+      <x:c r="D93" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E93" s="0" t="s">
+        <x:v>684</x:v>
+      </x:c>
+      <x:c r="F93" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G93" s="0" t="s">
+        <x:v>685</x:v>
+      </x:c>
+      <x:c r="H93" s="0" t="s">
+        <x:v>686</x:v>
+      </x:c>
+      <x:c r="I93" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J93" s="0" t="s">
+        <x:v>687</x:v>
+      </x:c>
+      <x:c r="K93" s="0" t="s">
+        <x:v>688</x:v>
+      </x:c>
+      <x:c r="N93" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" spans="1:14">
+      <x:c r="A94" s="0" t="s">
+        <x:v>689</x:v>
+      </x:c>
+      <x:c r="B94" s="0" t="s">
+        <x:v>690</x:v>
+      </x:c>
+      <x:c r="C94" s="0" t="s">
+        <x:v>691</x:v>
+      </x:c>
+      <x:c r="D94" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E94" s="0" t="s">
+        <x:v>692</x:v>
+      </x:c>
+      <x:c r="F94" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G94" s="0" t="s">
+        <x:v>693</x:v>
+      </x:c>
+      <x:c r="H94" s="0" t="s">
+        <x:v>694</x:v>
+      </x:c>
+      <x:c r="I94" s="0" t="s">
+        <x:v>695</x:v>
+      </x:c>
+      <x:c r="J94" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="K94" s="0" t="s">
+        <x:v>696</x:v>
+      </x:c>
+      <x:c r="N94" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" spans="1:14">
+      <x:c r="A95" s="0" t="s">
+        <x:v>697</x:v>
+      </x:c>
+      <x:c r="B95" s="0" t="s">
+        <x:v>698</x:v>
+      </x:c>
+      <x:c r="C95" s="0" t="s">
+        <x:v>699</x:v>
+      </x:c>
+      <x:c r="D95" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E95" s="0" t="s">
+        <x:v>700</x:v>
+      </x:c>
+      <x:c r="F95" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G95" s="0" t="s">
+        <x:v>701</x:v>
+      </x:c>
+      <x:c r="H95" s="0" t="s">
+        <x:v>411</x:v>
+      </x:c>
+      <x:c r="I95" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J95" s="0" t="s">
+        <x:v>383</x:v>
+      </x:c>
+      <x:c r="K95" s="0" t="s">
+        <x:v>702</x:v>
+      </x:c>
+      <x:c r="N95" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" spans="1:14">
+      <x:c r="A96" s="0" t="s">
+        <x:v>703</x:v>
+      </x:c>
+      <x:c r="B96" s="0" t="s">
+        <x:v>704</x:v>
+      </x:c>
+      <x:c r="C96" s="0" t="s">
+        <x:v>705</x:v>
+      </x:c>
+      <x:c r="D96" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E96" s="0" t="s">
+        <x:v>706</x:v>
+      </x:c>
+      <x:c r="F96" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G96" s="0" t="s">
+        <x:v>707</x:v>
+      </x:c>
+      <x:c r="H96" s="0" t="s">
+        <x:v>708</x:v>
+      </x:c>
+      <x:c r="I96" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J96" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="K96" s="0" t="s">
+        <x:v>709</x:v>
+      </x:c>
+      <x:c r="N96" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" spans="1:14">
+      <x:c r="A97" s="0" t="s">
+        <x:v>710</x:v>
+      </x:c>
+      <x:c r="B97" s="0" t="s">
+        <x:v>711</x:v>
+      </x:c>
+      <x:c r="C97" s="0" t="s">
+        <x:v>712</x:v>
+      </x:c>
+      <x:c r="D97" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E97" s="0" t="s">
+        <x:v>713</x:v>
+      </x:c>
+      <x:c r="F97" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G97" s="0" t="s">
+        <x:v>714</x:v>
+      </x:c>
+      <x:c r="H97" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="I97" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J97" s="0" t="s">
+        <x:v>715</x:v>
+      </x:c>
+      <x:c r="K97" s="0" t="s">
+        <x:v>716</x:v>
+      </x:c>
+      <x:c r="N97" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" spans="1:14">
+      <x:c r="A98" s="0" t="s">
+        <x:v>717</x:v>
+      </x:c>
+      <x:c r="B98" s="0" t="s">
+        <x:v>718</x:v>
+      </x:c>
+      <x:c r="C98" s="0" t="s">
+        <x:v>719</x:v>
+      </x:c>
+      <x:c r="D98" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E98" s="0" t="s">
+        <x:v>720</x:v>
+      </x:c>
+      <x:c r="F98" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G98" s="0" t="s">
+        <x:v>721</x:v>
+      </x:c>
+      <x:c r="H98" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="I98" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J98" s="0" t="s">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="K98" s="0" t="s">
+        <x:v>722</x:v>
+      </x:c>
+      <x:c r="N98" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" spans="1:14">
+      <x:c r="A99" s="0" t="s">
+        <x:v>723</x:v>
+      </x:c>
+      <x:c r="B99" s="0" t="s">
+        <x:v>724</x:v>
+      </x:c>
+      <x:c r="C99" s="0" t="s">
+        <x:v>725</x:v>
+      </x:c>
+      <x:c r="D99" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E99" s="0" t="s">
+        <x:v>726</x:v>
+      </x:c>
+      <x:c r="F99" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G99" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="H99" s="0" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="I99" s="0" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="J99" s="0" t="s">
+        <x:v>727</x:v>
+      </x:c>
+      <x:c r="K99" s="0" t="s">
+        <x:v>728</x:v>
+      </x:c>
+      <x:c r="N99" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" spans="1:14">
+      <x:c r="A100" s="0" t="s">
+        <x:v>729</x:v>
+      </x:c>
+      <x:c r="B100" s="0" t="s">
+        <x:v>730</x:v>
+      </x:c>
+      <x:c r="C100" s="0" t="s">
+        <x:v>731</x:v>
+      </x:c>
+      <x:c r="D100" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E100" s="0" t="s">
+        <x:v>732</x:v>
+      </x:c>
+      <x:c r="F100" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G100" s="0" t="s">
+        <x:v>733</x:v>
+      </x:c>
+      <x:c r="H100" s="0" t="s">
+        <x:v>734</x:v>
+      </x:c>
+      <x:c r="I100" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J100" s="0" t="s">
+        <x:v>679</x:v>
+      </x:c>
+      <x:c r="K100" s="0" t="s">
+        <x:v>735</x:v>
+      </x:c>
+      <x:c r="N100" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" spans="1:14">
+      <x:c r="A101" s="0" t="s">
+        <x:v>736</x:v>
+      </x:c>
+      <x:c r="B101" s="0" t="s">
+        <x:v>737</x:v>
+      </x:c>
+      <x:c r="C101" s="0" t="s">
+        <x:v>738</x:v>
+      </x:c>
+      <x:c r="D101" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E101" s="0" t="s">
+        <x:v>739</x:v>
+      </x:c>
+      <x:c r="F101" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G101" s="0" t="s">
+        <x:v>740</x:v>
+      </x:c>
+      <x:c r="H101" s="0" t="s">
+        <x:v>405</x:v>
+      </x:c>
+      <x:c r="I101" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J101" s="0" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="K101" s="0" t="s">
+        <x:v>741</x:v>
+      </x:c>
+      <x:c r="N101" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" spans="1:14">
+      <x:c r="A102" s="0" t="s">
+        <x:v>742</x:v>
+      </x:c>
+      <x:c r="B102" s="0" t="s">
+        <x:v>743</x:v>
+      </x:c>
+      <x:c r="C102" s="0" t="s">
+        <x:v>744</x:v>
+      </x:c>
+      <x:c r="D102" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E102" s="0" t="s">
+        <x:v>745</x:v>
+      </x:c>
+      <x:c r="F102" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G102" s="0" t="s">
+        <x:v>746</x:v>
+      </x:c>
+      <x:c r="H102" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="I102" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J102" s="0" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="K102" s="0" t="s">
+        <x:v>747</x:v>
+      </x:c>
+      <x:c r="N102" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" spans="1:14">
+      <x:c r="A103" s="0" t="s">
+        <x:v>748</x:v>
+      </x:c>
+      <x:c r="B103" s="0" t="s">
+        <x:v>749</x:v>
+      </x:c>
+      <x:c r="C103" s="0" t="s">
+        <x:v>750</x:v>
+      </x:c>
+      <x:c r="D103" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E103" s="0" t="s">
+        <x:v>751</x:v>
+      </x:c>
+      <x:c r="F103" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G103" s="0" t="s">
+        <x:v>752</x:v>
+      </x:c>
+      <x:c r="H103" s="0" t="s">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="I103" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J103" s="0" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="K103" s="0" t="s">
+        <x:v>753</x:v>
+      </x:c>
+      <x:c r="N103" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" spans="1:14">
+      <x:c r="A104" s="0" t="s">
+        <x:v>754</x:v>
+      </x:c>
+      <x:c r="B104" s="0" t="s">
+        <x:v>755</x:v>
+      </x:c>
+      <x:c r="C104" s="0" t="s">
+        <x:v>756</x:v>
+      </x:c>
+      <x:c r="D104" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E104" s="0" t="s">
+        <x:v>757</x:v>
+      </x:c>
+      <x:c r="F104" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G104" s="0" t="s">
+        <x:v>758</x:v>
+      </x:c>
+      <x:c r="H104" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="I104" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J104" s="0" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="K104" s="0" t="s">
+        <x:v>759</x:v>
+      </x:c>
+      <x:c r="N104" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" spans="1:14">
+      <x:c r="A105" s="0" t="s">
+        <x:v>760</x:v>
+      </x:c>
+      <x:c r="B105" s="0" t="s">
+        <x:v>761</x:v>
+      </x:c>
+      <x:c r="C105" s="0" t="s">
+        <x:v>762</x:v>
+      </x:c>
+      <x:c r="D105" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E105" s="0" t="s">
+        <x:v>763</x:v>
+      </x:c>
+      <x:c r="F105" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G105" s="0" t="s">
+        <x:v>764</x:v>
+      </x:c>
+      <x:c r="H105" s="0" t="s">
+        <x:v>765</x:v>
+      </x:c>
+      <x:c r="I105" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="J105" s="0" t="s">
+        <x:v>766</x:v>
+      </x:c>
+      <x:c r="K105" s="0" t="s">
+        <x:v>767</x:v>
+      </x:c>
+      <x:c r="N105" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" spans="1:14">
+      <x:c r="A106" s="0" t="s">
+        <x:v>768</x:v>
+      </x:c>
+      <x:c r="B106" s="0" t="s">
+        <x:v>769</x:v>
+      </x:c>
+      <x:c r="C106" s="0" t="s">
+        <x:v>770</x:v>
+      </x:c>
+      <x:c r="D106" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E106" s="0" t="s">
+        <x:v>771</x:v>
+      </x:c>
+      <x:c r="F106" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G106" s="0" t="s">
+        <x:v>772</x:v>
+      </x:c>
+      <x:c r="H106" s="0" t="s">
+        <x:v>405</x:v>
+      </x:c>
+      <x:c r="I106" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J106" s="0" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="K106" s="0" t="s">
+        <x:v>773</x:v>
+      </x:c>
+      <x:c r="N106" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107" spans="1:14">
+      <x:c r="A107" s="0" t="s">
+        <x:v>774</x:v>
+      </x:c>
+      <x:c r="B107" s="0" t="s">
+        <x:v>775</x:v>
+      </x:c>
+      <x:c r="C107" s="0" t="s">
+        <x:v>776</x:v>
+      </x:c>
+      <x:c r="D107" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E107" s="0" t="s">
+        <x:v>777</x:v>
+      </x:c>
+      <x:c r="F107" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G107" s="0" t="s">
+        <x:v>778</x:v>
+      </x:c>
+      <x:c r="H107" s="0" t="s">
+        <x:v>779</x:v>
+      </x:c>
+      <x:c r="I107" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="J107" s="0" t="s">
+        <x:v>780</x:v>
+      </x:c>
+      <x:c r="K107" s="0" t="s">
+        <x:v>781</x:v>
+      </x:c>
+      <x:c r="N107" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" spans="1:14">
+      <x:c r="A108" s="0" t="s">
+        <x:v>782</x:v>
+      </x:c>
+      <x:c r="B108" s="0" t="s">
+        <x:v>783</x:v>
+      </x:c>
+      <x:c r="C108" s="0" t="s">
+        <x:v>784</x:v>
+      </x:c>
+      <x:c r="D108" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E108" s="0" t="s">
+        <x:v>785</x:v>
+      </x:c>
+      <x:c r="F108" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G108" s="0" t="s">
+        <x:v>786</x:v>
+      </x:c>
+      <x:c r="H108" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="I108" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J108" s="0" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="K108" s="0" t="s">
+        <x:v>787</x:v>
+      </x:c>
+      <x:c r="N108" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" spans="1:14">
+      <x:c r="A109" s="0" t="s">
+        <x:v>788</x:v>
+      </x:c>
+      <x:c r="B109" s="0" t="s">
+        <x:v>789</x:v>
+      </x:c>
+      <x:c r="C109" s="0" t="s">
+        <x:v>790</x:v>
+      </x:c>
+      <x:c r="D109" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E109" s="0" t="s">
+        <x:v>791</x:v>
+      </x:c>
+      <x:c r="F109" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G109" s="0" t="s">
+        <x:v>792</x:v>
+      </x:c>
+      <x:c r="H109" s="0" t="s">
+        <x:v>793</x:v>
+      </x:c>
+      <x:c r="I109" s="0" t="s">
+        <x:v>501</x:v>
+      </x:c>
+      <x:c r="J109" s="0" t="s">
+        <x:v>794</x:v>
+      </x:c>
+      <x:c r="K109" s="0" t="s">
+        <x:v>795</x:v>
+      </x:c>
+      <x:c r="N109" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" spans="1:14">
+      <x:c r="A110" s="0" t="s">
+        <x:v>796</x:v>
+      </x:c>
+      <x:c r="B110" s="0" t="s">
+        <x:v>797</x:v>
+      </x:c>
+      <x:c r="C110" s="0" t="s">
+        <x:v>798</x:v>
+      </x:c>
+      <x:c r="D110" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E110" s="0" t="s">
+        <x:v>799</x:v>
+      </x:c>
+      <x:c r="F110" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G110" s="0" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="H110" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="I110" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J110" s="0" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="K110" s="0" t="s">
+        <x:v>800</x:v>
+      </x:c>
+      <x:c r="N110" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" spans="1:14">
+      <x:c r="A111" s="0" t="s">
+        <x:v>801</x:v>
+      </x:c>
+      <x:c r="B111" s="0" t="s">
+        <x:v>802</x:v>
+      </x:c>
+      <x:c r="C111" s="0" t="s">
+        <x:v>803</x:v>
+      </x:c>
+      <x:c r="D111" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E111" s="0" t="s">
+        <x:v>804</x:v>
+      </x:c>
+      <x:c r="F111" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G111" s="0" t="s">
+        <x:v>805</x:v>
+      </x:c>
+      <x:c r="H111" s="0" t="s">
+        <x:v>806</x:v>
+      </x:c>
+      <x:c r="I111" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J111" s="0" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="K111" s="0" t="s">
+        <x:v>807</x:v>
+      </x:c>
+      <x:c r="N111" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" spans="1:14">
+      <x:c r="A112" s="0" t="s">
+        <x:v>808</x:v>
+      </x:c>
+      <x:c r="B112" s="0" t="s">
+        <x:v>809</x:v>
+      </x:c>
+      <x:c r="C112" s="0" t="s">
+        <x:v>810</x:v>
+      </x:c>
+      <x:c r="D112" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E112" s="0" t="s">
+        <x:v>811</x:v>
+      </x:c>
+      <x:c r="F112" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G112" s="0" t="s">
+        <x:v>812</x:v>
+      </x:c>
+      <x:c r="H112" s="0" t="s">
+        <x:v>813</x:v>
+      </x:c>
+      <x:c r="I112" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J112" s="0" t="s">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="K112" s="0" t="s">
+        <x:v>814</x:v>
+      </x:c>
+      <x:c r="N112" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" spans="1:14">
+      <x:c r="A113" s="0" t="s">
+        <x:v>815</x:v>
+      </x:c>
+      <x:c r="B113" s="0" t="s">
+        <x:v>816</x:v>
+      </x:c>
+      <x:c r="C113" s="0" t="s">
+        <x:v>817</x:v>
+      </x:c>
+      <x:c r="D113" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E113" s="0" t="s">
+        <x:v>818</x:v>
+      </x:c>
+      <x:c r="F113" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G113" s="0" t="s">
+        <x:v>819</x:v>
+      </x:c>
+      <x:c r="H113" s="0" t="s">
+        <x:v>820</x:v>
+      </x:c>
+      <x:c r="I113" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J113" s="0" t="s">
+        <x:v>780</x:v>
+      </x:c>
+      <x:c r="K113" s="0" t="s">
+        <x:v>821</x:v>
+      </x:c>
+      <x:c r="N113" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" spans="1:14">
+      <x:c r="A114" s="0" t="s">
+        <x:v>822</x:v>
+      </x:c>
+      <x:c r="B114" s="0" t="s">
+        <x:v>823</x:v>
+      </x:c>
+      <x:c r="C114" s="0" t="s">
+        <x:v>824</x:v>
+      </x:c>
+      <x:c r="D114" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E114" s="0" t="s">
+        <x:v>825</x:v>
+      </x:c>
+      <x:c r="F114" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G114" s="0" t="s">
+        <x:v>826</x:v>
+      </x:c>
+      <x:c r="H114" s="0" t="s">
+        <x:v>827</x:v>
+      </x:c>
+      <x:c r="I114" s="0" t="s">
+        <x:v>501</x:v>
+      </x:c>
+      <x:c r="J114" s="0" t="s">
+        <x:v>828</x:v>
+      </x:c>
+      <x:c r="K114" s="0" t="s">
+        <x:v>829</x:v>
+      </x:c>
+      <x:c r="N114" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" spans="1:14">
+      <x:c r="A115" s="0" t="s">
+        <x:v>830</x:v>
+      </x:c>
+      <x:c r="B115" s="0" t="s">
+        <x:v>831</x:v>
+      </x:c>
+      <x:c r="C115" s="0" t="s">
+        <x:v>832</x:v>
+      </x:c>
+      <x:c r="D115" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E115" s="0" t="s">
+        <x:v>833</x:v>
+      </x:c>
+      <x:c r="F115" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G115" s="0" t="s">
+        <x:v>834</x:v>
+      </x:c>
+      <x:c r="H115" s="0" t="s">
+        <x:v>694</x:v>
+      </x:c>
+      <x:c r="I115" s="0" t="s">
+        <x:v>695</x:v>
+      </x:c>
+      <x:c r="N115" s="0" t="s">
+        <x:v>835</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" spans="1:14">
+      <x:c r="A116" s="0" t="s">
+        <x:v>836</x:v>
+      </x:c>
+      <x:c r="B116" s="0" t="s">
+        <x:v>837</x:v>
+      </x:c>
+      <x:c r="C116" s="0" t="s">
+        <x:v>838</x:v>
+      </x:c>
+      <x:c r="D116" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E116" s="0" t="s">
+        <x:v>839</x:v>
+      </x:c>
+      <x:c r="F116" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G116" s="0" t="s">
+        <x:v>840</x:v>
+      </x:c>
+      <x:c r="H116" s="0" t="s">
+        <x:v>841</x:v>
+      </x:c>
+      <x:c r="I116" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="N116" s="0" t="s">
+        <x:v>835</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" spans="1:14">
+      <x:c r="A117" s="0" t="s">
+        <x:v>842</x:v>
+      </x:c>
+      <x:c r="B117" s="0" t="s">
+        <x:v>843</x:v>
+      </x:c>
+      <x:c r="C117" s="0" t="s">
+        <x:v>844</x:v>
+      </x:c>
+      <x:c r="D117" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E117" s="0" t="s">
+        <x:v>845</x:v>
+      </x:c>
+      <x:c r="F117" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G117" s="0" t="s">
+        <x:v>846</x:v>
+      </x:c>
+      <x:c r="H117" s="0" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="I117" s="0" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="N117" s="0" t="s">
+        <x:v>835</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" spans="1:14">
+      <x:c r="A118" s="0" t="s">
+        <x:v>847</x:v>
+      </x:c>
+      <x:c r="B118" s="0" t="s">
+        <x:v>848</x:v>
+      </x:c>
+      <x:c r="C118" s="0" t="s">
+        <x:v>849</x:v>
+      </x:c>
+      <x:c r="D118" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E118" s="0" t="s">
+        <x:v>850</x:v>
+      </x:c>
+      <x:c r="F118" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G118" s="0" t="s">
+        <x:v>851</x:v>
+      </x:c>
+      <x:c r="H118" s="0" t="s">
+        <x:v>672</x:v>
+      </x:c>
+      <x:c r="I118" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="J118" s="0" t="s">
+        <x:v>852</x:v>
+      </x:c>
+      <x:c r="K118" s="0" t="s">
+        <x:v>853</x:v>
+      </x:c>
+      <x:c r="N118" s="0" t="s">
+        <x:v>835</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119" spans="1:14">
+      <x:c r="A119" s="0" t="s">
+        <x:v>854</x:v>
+      </x:c>
+      <x:c r="B119" s="0" t="s">
+        <x:v>855</x:v>
+      </x:c>
+      <x:c r="C119" s="0" t="s">
+        <x:v>856</x:v>
+      </x:c>
+      <x:c r="D119" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E119" s="0" t="s">
+        <x:v>857</x:v>
+      </x:c>
+      <x:c r="F119" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G119" s="0" t="s">
+        <x:v>858</x:v>
+      </x:c>
+      <x:c r="H119" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="I119" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J119" s="0" t="s">
+        <x:v>859</x:v>
+      </x:c>
+      <x:c r="K119" s="0" t="s">
+        <x:v>860</x:v>
+      </x:c>
+      <x:c r="N119" s="0" t="s">
+        <x:v>835</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" spans="1:14">
+      <x:c r="A120" s="0" t="s">
+        <x:v>861</x:v>
+      </x:c>
+      <x:c r="B120" s="0" t="s">
+        <x:v>862</x:v>
+      </x:c>
+      <x:c r="C120" s="0" t="s">
+        <x:v>863</x:v>
+      </x:c>
+      <x:c r="D120" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E120" s="0" t="s">
+        <x:v>864</x:v>
+      </x:c>
+      <x:c r="F120" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G120" s="0" t="s">
+        <x:v>865</x:v>
+      </x:c>
+      <x:c r="H120" s="0" t="s">
+        <x:v>866</x:v>
+      </x:c>
+      <x:c r="I120" s="0" t="s">
+        <x:v>494</x:v>
+      </x:c>
+      <x:c r="J120" s="0" t="s">
+        <x:v>867</x:v>
+      </x:c>
+      <x:c r="K120" s="0" t="s">
+        <x:v>868</x:v>
+      </x:c>
+      <x:c r="N120" s="0" t="s">
+        <x:v>835</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121" spans="1:14">
+      <x:c r="A121" s="0" t="s">
+        <x:v>869</x:v>
+      </x:c>
+      <x:c r="B121" s="0" t="s">
+        <x:v>870</x:v>
+      </x:c>
+      <x:c r="C121" s="0" t="s">
+        <x:v>871</x:v>
+      </x:c>
+      <x:c r="D121" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E121" s="0" t="s">
+        <x:v>872</x:v>
+      </x:c>
+      <x:c r="F121" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G121" s="0" t="s">
+        <x:v>873</x:v>
+      </x:c>
+      <x:c r="H121" s="0" t="s">
+        <x:v>874</x:v>
+      </x:c>
+      <x:c r="I121" s="0" t="s">
+        <x:v>501</x:v>
+      </x:c>
+      <x:c r="J121" s="0" t="s">
+        <x:v>875</x:v>
+      </x:c>
+      <x:c r="K121" s="0" t="s">
+        <x:v>876</x:v>
+      </x:c>
+      <x:c r="N121" s="0" t="s">
+        <x:v>835</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122" spans="1:14">
+      <x:c r="A122" s="0" t="s">
+        <x:v>877</x:v>
+      </x:c>
+      <x:c r="B122" s="0" t="s">
+        <x:v>878</x:v>
+      </x:c>
+      <x:c r="C122" s="0" t="s">
+        <x:v>879</x:v>
+      </x:c>
+      <x:c r="D122" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E122" s="0" t="s">
+        <x:v>880</x:v>
+      </x:c>
+      <x:c r="F122" s="0" t="s">
+        <x:v>881</x:v>
+      </x:c>
+      <x:c r="G122" s="0" t="s">
+        <x:v>882</x:v>
+      </x:c>
+      <x:c r="H122" s="0" t="s">
+        <x:v>883</x:v>
+      </x:c>
+      <x:c r="I122" s="0" t="s">
+        <x:v>501</x:v>
+      </x:c>
+      <x:c r="J122" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="K122" s="0" t="s">
+        <x:v>884</x:v>
+      </x:c>
+      <x:c r="N122" s="0" t="s">
+        <x:v>885</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" spans="1:14">
+      <x:c r="A123" s="0" t="s">
+        <x:v>886</x:v>
+      </x:c>
+      <x:c r="B123" s="0" t="s">
+        <x:v>887</x:v>
+      </x:c>
+      <x:c r="C123" s="0" t="s">
+        <x:v>888</x:v>
+      </x:c>
+      <x:c r="D123" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E123" s="0" t="s">
+        <x:v>889</x:v>
+      </x:c>
+      <x:c r="F123" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G123" s="0" t="s">
+        <x:v>890</x:v>
+      </x:c>
+      <x:c r="H123" s="0" t="s">
+        <x:v>891</x:v>
+      </x:c>
+      <x:c r="I123" s="0" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="J123" s="0" t="s">
+        <x:v>828</x:v>
+      </x:c>
+      <x:c r="K123" s="0" t="s">
+        <x:v>892</x:v>
+      </x:c>
+      <x:c r="N123" s="0" t="s">
+        <x:v>885</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124" spans="1:14">
+      <x:c r="A124" s="0" t="s">
+        <x:v>893</x:v>
+      </x:c>
+      <x:c r="B124" s="0" t="s">
+        <x:v>894</x:v>
+      </x:c>
+      <x:c r="C124" s="0" t="s">
+        <x:v>895</x:v>
+      </x:c>
+      <x:c r="D124" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E124" s="0" t="s">
+        <x:v>896</x:v>
+      </x:c>
+      <x:c r="F124" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G124" s="0" t="s">
+        <x:v>897</x:v>
+      </x:c>
+      <x:c r="H124" s="0" t="s">
+        <x:v>898</x:v>
+      </x:c>
+      <x:c r="I124" s="0" t="s">
+        <x:v>695</x:v>
+      </x:c>
+      <x:c r="J124" s="0" t="s">
+        <x:v>899</x:v>
+      </x:c>
+      <x:c r="K124" s="0" t="s">
+        <x:v>900</x:v>
+      </x:c>
+      <x:c r="N124" s="0" t="s">
+        <x:v>885</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125" spans="1:14">
+      <x:c r="A125" s="0" t="s">
+        <x:v>901</x:v>
+      </x:c>
+      <x:c r="B125" s="0" t="s">
+        <x:v>902</x:v>
+      </x:c>
+      <x:c r="C125" s="0" t="s">
+        <x:v>903</x:v>
+      </x:c>
+      <x:c r="D125" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E125" s="0" t="s">
+        <x:v>904</x:v>
+      </x:c>
+      <x:c r="F125" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G125" s="0" t="s">
+        <x:v>905</x:v>
+      </x:c>
+      <x:c r="H125" s="0" t="s">
+        <x:v>906</x:v>
+      </x:c>
+      <x:c r="I125" s="0" t="s">
+        <x:v>501</x:v>
+      </x:c>
+      <x:c r="J125" s="0" t="s">
+        <x:v>907</x:v>
+      </x:c>
+      <x:c r="K125" s="0" t="s">
+        <x:v>908</x:v>
+      </x:c>
+      <x:c r="N125" s="0" t="s">
+        <x:v>885</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126" spans="1:14">
+      <x:c r="A126" s="0" t="s">
+        <x:v>909</x:v>
+      </x:c>
+      <x:c r="B126" s="0" t="s">
+        <x:v>910</x:v>
+      </x:c>
+      <x:c r="C126" s="0" t="s">
+        <x:v>911</x:v>
+      </x:c>
+      <x:c r="D126" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E126" s="0" t="s">
+        <x:v>912</x:v>
+      </x:c>
+      <x:c r="F126" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G126" s="0" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="H126" s="0" t="s">
+        <x:v>467</x:v>
+      </x:c>
+      <x:c r="I126" s="0" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="J126" s="0" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="K126" s="0" t="s">
+        <x:v>913</x:v>
+      </x:c>
+      <x:c r="N126" s="0" t="s">
+        <x:v>885</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127" spans="1:14">
+      <x:c r="A127" s="0" t="s">
+        <x:v>914</x:v>
+      </x:c>
+      <x:c r="B127" s="0" t="s">
+        <x:v>915</x:v>
+      </x:c>
+      <x:c r="C127" s="0" t="s">
+        <x:v>916</x:v>
+      </x:c>
+      <x:c r="D127" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E127" s="0" t="s">
+        <x:v>917</x:v>
+      </x:c>
+      <x:c r="F127" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G127" s="0" t="s">
+        <x:v>622</x:v>
+      </x:c>
+      <x:c r="H127" s="0" t="s">
+        <x:v>918</x:v>
+      </x:c>
+      <x:c r="I127" s="0" t="s">
+        <x:v>501</x:v>
+      </x:c>
+      <x:c r="J127" s="0" t="s">
+        <x:v>919</x:v>
+      </x:c>
+      <x:c r="K127" s="0" t="s">
+        <x:v>920</x:v>
+      </x:c>
+      <x:c r="N127" s="0" t="s">
+        <x:v>885</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128" spans="1:14">
+      <x:c r="A128" s="0" t="s">
+        <x:v>921</x:v>
+      </x:c>
+      <x:c r="B128" s="0" t="s">
+        <x:v>922</x:v>
+      </x:c>
+      <x:c r="C128" s="0" t="s">
+        <x:v>923</x:v>
+      </x:c>
+      <x:c r="D128" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E128" s="0" t="s">
+        <x:v>924</x:v>
+      </x:c>
+      <x:c r="F128" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G128" s="0" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="H128" s="0" t="s">
+        <x:v>467</x:v>
+      </x:c>
+      <x:c r="I128" s="0" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="J128" s="0" t="s">
+        <x:v>727</x:v>
+      </x:c>
+      <x:c r="K128" s="0" t="s">
+        <x:v>925</x:v>
+      </x:c>
+      <x:c r="N128" s="0" t="s">
+        <x:v>885</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129" spans="1:14">
+      <x:c r="A129" s="0" t="s">
+        <x:v>926</x:v>
+      </x:c>
+      <x:c r="B129" s="0" t="s">
+        <x:v>927</x:v>
+      </x:c>
+      <x:c r="C129" s="0" t="s">
+        <x:v>928</x:v>
+      </x:c>
+      <x:c r="D129" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E129" s="0" t="s">
+        <x:v>929</x:v>
+      </x:c>
+      <x:c r="F129" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G129" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="H129" s="0" t="s">
+        <x:v>930</x:v>
+      </x:c>
+      <x:c r="I129" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="J129" s="0" t="s">
+        <x:v>828</x:v>
+      </x:c>
+      <x:c r="K129" s="0" t="s">
+        <x:v>931</x:v>
+      </x:c>
+      <x:c r="N129" s="0" t="s">
+        <x:v>932</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130" spans="1:14">
+      <x:c r="A130" s="0" t="s">
+        <x:v>933</x:v>
+      </x:c>
+      <x:c r="B130" s="0" t="s">
+        <x:v>934</x:v>
+      </x:c>
+      <x:c r="C130" s="0" t="s">
+        <x:v>935</x:v>
+      </x:c>
+      <x:c r="D130" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E130" s="0" t="s">
+        <x:v>936</x:v>
+      </x:c>
+      <x:c r="F130" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G130" s="0" t="s">
+        <x:v>937</x:v>
+      </x:c>
+      <x:c r="H130" s="0" t="s">
+        <x:v>813</x:v>
+      </x:c>
+      <x:c r="I130" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J130" s="0" t="s">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="K130" s="0" t="s">
+        <x:v>938</x:v>
+      </x:c>
+      <x:c r="N130" s="0" t="s">
+        <x:v>932</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131" spans="1:14">
+      <x:c r="A131" s="0" t="s">
+        <x:v>939</x:v>
+      </x:c>
+      <x:c r="B131" s="0" t="s">
+        <x:v>940</x:v>
+      </x:c>
+      <x:c r="C131" s="0" t="s">
+        <x:v>941</x:v>
+      </x:c>
+      <x:c r="D131" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E131" s="0" t="s">
+        <x:v>942</x:v>
+      </x:c>
+      <x:c r="F131" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G131" s="0" t="s">
+        <x:v>943</x:v>
+      </x:c>
+      <x:c r="H131" s="0" t="s">
+        <x:v>944</x:v>
+      </x:c>
+      <x:c r="I131" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="J131" s="0" t="s">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="K131" s="0" t="s">
+        <x:v>945</x:v>
+      </x:c>
+      <x:c r="N131" s="0" t="s">
+        <x:v>932</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132" spans="1:14">
+      <x:c r="A132" s="0" t="s">
+        <x:v>946</x:v>
+      </x:c>
+      <x:c r="B132" s="0" t="s">
+        <x:v>947</x:v>
+      </x:c>
+      <x:c r="C132" s="0" t="s">
+        <x:v>948</x:v>
+      </x:c>
+      <x:c r="D132" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E132" s="0" t="s">
+        <x:v>949</x:v>
+      </x:c>
+      <x:c r="F132" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G132" s="0" t="s">
+        <x:v>950</x:v>
+      </x:c>
+      <x:c r="H132" s="0" t="s">
+        <x:v>951</x:v>
+      </x:c>
+      <x:c r="I132" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J132" s="0" t="s">
+        <x:v>952</x:v>
+      </x:c>
+      <x:c r="K132" s="0" t="s">
+        <x:v>953</x:v>
+      </x:c>
+      <x:c r="N132" s="0" t="s">
+        <x:v>932</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133" spans="1:14">
+      <x:c r="A133" s="0" t="s">
+        <x:v>954</x:v>
+      </x:c>
+      <x:c r="B133" s="0" t="s">
+        <x:v>955</x:v>
+      </x:c>
+      <x:c r="C133" s="0" t="s">
+        <x:v>956</x:v>
+      </x:c>
+      <x:c r="D133" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E133" s="0" t="s">
+        <x:v>957</x:v>
+      </x:c>
+      <x:c r="F133" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G133" s="0" t="s">
+        <x:v>958</x:v>
+      </x:c>
+      <x:c r="H133" s="0" t="s">
+        <x:v>959</x:v>
+      </x:c>
+      <x:c r="I133" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="N133" s="0" t="s">
+        <x:v>960</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134" spans="1:14">
+      <x:c r="A134" s="0" t="s">
+        <x:v>961</x:v>
+      </x:c>
+      <x:c r="B134" s="0" t="s">
+        <x:v>962</x:v>
+      </x:c>
+      <x:c r="C134" s="0" t="s">
+        <x:v>963</x:v>
+      </x:c>
+      <x:c r="D134" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E134" s="0" t="s">
+        <x:v>964</x:v>
+      </x:c>
+      <x:c r="F134" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G134" s="0" t="s">
+        <x:v>965</x:v>
+      </x:c>
+      <x:c r="H134" s="0" t="s">
+        <x:v>966</x:v>
+      </x:c>
+      <x:c r="I134" s="0" t="s">
+        <x:v>967</x:v>
+      </x:c>
+      <x:c r="J134" s="0" t="s">
+        <x:v>919</x:v>
+      </x:c>
+      <x:c r="K134" s="0" t="s">
+        <x:v>968</x:v>
+      </x:c>
+      <x:c r="N134" s="0" t="s">
+        <x:v>960</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135" spans="1:14">
+      <x:c r="A135" s="0" t="s">
+        <x:v>969</x:v>
+      </x:c>
+      <x:c r="B135" s="0" t="s">
+        <x:v>970</x:v>
+      </x:c>
+      <x:c r="C135" s="0" t="s">
+        <x:v>971</x:v>
+      </x:c>
+      <x:c r="D135" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E135" s="0" t="s">
+        <x:v>972</x:v>
+      </x:c>
+      <x:c r="F135" s="0" t="s">
+        <x:v>973</x:v>
+      </x:c>
+      <x:c r="G135" s="0" t="s">
+        <x:v>974</x:v>
+      </x:c>
+      <x:c r="H135" s="0" t="s">
+        <x:v>975</x:v>
+      </x:c>
+      <x:c r="I135" s="0" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="J135" s="0" t="s">
+        <x:v>417</x:v>
+      </x:c>
+      <x:c r="K135" s="0" t="s">
+        <x:v>976</x:v>
+      </x:c>
+      <x:c r="N135" s="0" t="s">
+        <x:v>977</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136" spans="1:14">
+      <x:c r="A136" s="0" t="s">
+        <x:v>978</x:v>
+      </x:c>
+      <x:c r="B136" s="0" t="s">
+        <x:v>979</x:v>
+      </x:c>
+      <x:c r="C136" s="0" t="s">
+        <x:v>980</x:v>
+      </x:c>
+      <x:c r="D136" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E136" s="0" t="s">
+        <x:v>981</x:v>
+      </x:c>
+      <x:c r="F136" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G136" s="0" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="H136" s="0" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="I136" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="N136" s="0" t="s">
+        <x:v>977</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137" spans="1:14">
+      <x:c r="A137" s="0" t="s">
+        <x:v>982</x:v>
+      </x:c>
+      <x:c r="B137" s="0" t="s">
+        <x:v>983</x:v>
+      </x:c>
+      <x:c r="C137" s="0" t="s">
+        <x:v>984</x:v>
+      </x:c>
+      <x:c r="D137" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E137" s="0" t="s">
+        <x:v>985</x:v>
+      </x:c>
+      <x:c r="F137" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G137" s="0" t="s">
+        <x:v>986</x:v>
+      </x:c>
+      <x:c r="H137" s="0" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="I137" s="0" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="J137" s="0" t="s">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="K137" s="0" t="s">
+        <x:v>987</x:v>
+      </x:c>
+      <x:c r="N137" s="0" t="s">
+        <x:v>988</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138" spans="1:14">
+      <x:c r="A138" s="0" t="s">
+        <x:v>989</x:v>
+      </x:c>
+      <x:c r="B138" s="0" t="s">
+        <x:v>990</x:v>
+      </x:c>
+      <x:c r="C138" s="0" t="s">
+        <x:v>991</x:v>
+      </x:c>
+      <x:c r="D138" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E138" s="0" t="s">
+        <x:v>992</x:v>
+      </x:c>
+      <x:c r="F138" s="0" t="s">
+        <x:v>993</x:v>
+      </x:c>
+      <x:c r="G138" s="0" t="s">
+        <x:v>994</x:v>
+      </x:c>
+      <x:c r="H138" s="0" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="I138" s="0" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="J138" s="0" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="K138" s="0" t="s">
+        <x:v>995</x:v>
+      </x:c>
+      <x:c r="N138" s="0" t="s">
+        <x:v>996</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139" spans="1:14">
+      <x:c r="A139" s="0" t="s">
+        <x:v>997</x:v>
+      </x:c>
+      <x:c r="B139" s="0" t="s">
+        <x:v>998</x:v>
+      </x:c>
+      <x:c r="C139" s="0" t="s">
+        <x:v>999</x:v>
+      </x:c>
+      <x:c r="D139" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E139" s="0" t="s">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="F139" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G139" s="0" t="s">
+        <x:v>448</x:v>
+      </x:c>
+      <x:c r="H139" s="0" t="s">
+        <x:v>1001</x:v>
+      </x:c>
+      <x:c r="I139" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="N139" s="0" t="s">
+        <x:v>1002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140" spans="1:14">
+      <x:c r="A140" s="0" t="s">
+        <x:v>1003</x:v>
+      </x:c>
+      <x:c r="B140" s="0" t="s">
+        <x:v>1004</x:v>
+      </x:c>
+      <x:c r="C140" s="0" t="s">
+        <x:v>1005</x:v>
+      </x:c>
+      <x:c r="D140" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E140" s="0" t="s">
+        <x:v>1006</x:v>
+      </x:c>
+      <x:c r="F140" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G140" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="H140" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="I140" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="N140" s="0" t="s">
+        <x:v>1002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141" spans="1:14">
+      <x:c r="A141" s="0" t="s">
+        <x:v>1007</x:v>
+      </x:c>
+      <x:c r="B141" s="0" t="s">
+        <x:v>1008</x:v>
+      </x:c>
+      <x:c r="C141" s="0" t="s">
+        <x:v>1009</x:v>
+      </x:c>
+      <x:c r="D141" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E141" s="0" t="s">
+        <x:v>1010</x:v>
+      </x:c>
+      <x:c r="F141" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G141" s="0" t="s">
+        <x:v>1011</x:v>
+      </x:c>
+      <x:c r="H141" s="0" t="s">
+        <x:v>637</x:v>
+      </x:c>
+      <x:c r="I141" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="N141" s="0" t="s">
+        <x:v>1002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142" spans="1:14">
+      <x:c r="A142" s="0" t="s">
+        <x:v>1012</x:v>
+      </x:c>
+      <x:c r="B142" s="0" t="s">
+        <x:v>1013</x:v>
+      </x:c>
+      <x:c r="C142" s="0" t="s">
+        <x:v>1014</x:v>
+      </x:c>
+      <x:c r="D142" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E142" s="0" t="s">
+        <x:v>1015</x:v>
+      </x:c>
+      <x:c r="F142" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G142" s="0" t="s">
+        <x:v>1016</x:v>
+      </x:c>
+      <x:c r="H142" s="0" t="s">
+        <x:v>1017</x:v>
+      </x:c>
+      <x:c r="I142" s="0" t="s">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="N142" s="0" t="s">
+        <x:v>1002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143" spans="1:14">
+      <x:c r="A143" s="0" t="s">
+        <x:v>1018</x:v>
+      </x:c>
+      <x:c r="B143" s="0" t="s">
+        <x:v>1019</x:v>
+      </x:c>
+      <x:c r="C143" s="0" t="s">
+        <x:v>1020</x:v>
+      </x:c>
+      <x:c r="D143" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E143" s="0" t="s">
+        <x:v>1021</x:v>
+      </x:c>
+      <x:c r="F143" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G143" s="0" t="s">
+        <x:v>1022</x:v>
+      </x:c>
+      <x:c r="H143" s="0" t="s">
+        <x:v>686</x:v>
+      </x:c>
+      <x:c r="I143" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="N143" s="0" t="s">
+        <x:v>1023</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144" spans="1:14">
+      <x:c r="A144" s="0" t="s">
+        <x:v>1024</x:v>
+      </x:c>
+      <x:c r="B144" s="0" t="s">
+        <x:v>1025</x:v>
+      </x:c>
+      <x:c r="C144" s="0" t="s">
+        <x:v>1026</x:v>
+      </x:c>
+      <x:c r="D144" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E144" s="0" t="s">
+        <x:v>1027</x:v>
+      </x:c>
+      <x:c r="F144" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G144" s="0" t="s">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="H144" s="0" t="s">
+        <x:v>1028</x:v>
+      </x:c>
+      <x:c r="I144" s="0" t="s">
+        <x:v>494</x:v>
+      </x:c>
+      <x:c r="J144" s="0" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="K144" s="0" t="s">
+        <x:v>1029</x:v>
+      </x:c>
+      <x:c r="N144" s="0" t="s">
+        <x:v>1030</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145" spans="1:14">
+      <x:c r="A145" s="0" t="s">
+        <x:v>1031</x:v>
+      </x:c>
+      <x:c r="B145" s="0" t="s">
+        <x:v>1032</x:v>
+      </x:c>
+      <x:c r="C145" s="0" t="s">
+        <x:v>1033</x:v>
+      </x:c>
+      <x:c r="D145" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E145" s="0" t="s">
+        <x:v>1034</x:v>
+      </x:c>
+      <x:c r="F145" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G145" s="0" t="s">
+        <x:v>1035</x:v>
+      </x:c>
+      <x:c r="H145" s="0" t="s">
+        <x:v>1036</x:v>
+      </x:c>
+      <x:c r="I145" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="J145" s="0" t="s">
+        <x:v>1037</x:v>
+      </x:c>
+      <x:c r="K145" s="0" t="s">
+        <x:v>1038</x:v>
+      </x:c>
+      <x:c r="N145" s="0" t="s">
+        <x:v>1039</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146" spans="1:14">
+      <x:c r="A146" s="0" t="s">
+        <x:v>1040</x:v>
+      </x:c>
+      <x:c r="B146" s="0" t="s">
+        <x:v>1041</x:v>
+      </x:c>
+      <x:c r="C146" s="0" t="s">
+        <x:v>1042</x:v>
+      </x:c>
+      <x:c r="D146" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E146" s="0" t="s">
+        <x:v>1043</x:v>
+      </x:c>
+      <x:c r="F146" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G146" s="0" t="s">
+        <x:v>1044</x:v>
+      </x:c>
+      <x:c r="H146" s="0" t="s">
+        <x:v>1045</x:v>
+      </x:c>
+      <x:c r="I146" s="0" t="s">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="N146" s="0" t="s">
+        <x:v>1039</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147" spans="1:14">
+      <x:c r="A147" s="0" t="s">
+        <x:v>1046</x:v>
+      </x:c>
+      <x:c r="B147" s="0" t="s">
+        <x:v>1047</x:v>
+      </x:c>
+      <x:c r="C147" s="0" t="s">
+        <x:v>1048</x:v>
+      </x:c>
+      <x:c r="D147" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E147" s="0" t="s">
+        <x:v>1049</x:v>
+      </x:c>
+      <x:c r="F147" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G147" s="0" t="s">
+        <x:v>435</x:v>
+      </x:c>
+      <x:c r="H147" s="0" t="s">
+        <x:v>1050</x:v>
+      </x:c>
+      <x:c r="I147" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="N147" s="0" t="s">
+        <x:v>1051</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148" spans="1:14">
+      <x:c r="A148" s="0" t="s">
+        <x:v>1052</x:v>
+      </x:c>
+      <x:c r="B148" s="0" t="s">
+        <x:v>1053</x:v>
+      </x:c>
+      <x:c r="C148" s="0" t="s">
+        <x:v>1054</x:v>
+      </x:c>
+      <x:c r="D148" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E148" s="0" t="s">
+        <x:v>1055</x:v>
+      </x:c>
+      <x:c r="F148" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G148" s="0" t="s">
+        <x:v>1022</x:v>
+      </x:c>
+      <x:c r="H148" s="0" t="s">
+        <x:v>1056</x:v>
+      </x:c>
+      <x:c r="I148" s="0" t="s">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="J148" s="0" t="s">
+        <x:v>1057</x:v>
+      </x:c>
+      <x:c r="K148" s="0" t="s">
+        <x:v>1058</x:v>
+      </x:c>
+      <x:c r="N148" s="0" t="s">
+        <x:v>1051</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149" spans="1:14">
+      <x:c r="A149" s="0" t="s">
+        <x:v>1059</x:v>
+      </x:c>
+      <x:c r="B149" s="0" t="s">
+        <x:v>1060</x:v>
+      </x:c>
+      <x:c r="C149" s="0" t="s">
+        <x:v>1061</x:v>
+      </x:c>
+      <x:c r="D149" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E149" s="0" t="s">
+        <x:v>1062</x:v>
+      </x:c>
+      <x:c r="F149" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G149" s="0" t="s">
+        <x:v>1063</x:v>
+      </x:c>
+      <x:c r="H149" s="0" t="s">
+        <x:v>472</x:v>
+      </x:c>
+      <x:c r="I149" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="N149" s="0" t="s">
+        <x:v>1064</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150" spans="1:14">
+      <x:c r="A150" s="0" t="s">
+        <x:v>1065</x:v>
+      </x:c>
+      <x:c r="B150" s="0" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="C150" s="0" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="D150" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E150" s="0" t="s">
+        <x:v>1066</x:v>
+      </x:c>
+      <x:c r="F150" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G150" s="0" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="H150" s="0" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="I150" s="0" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="N150" s="0" t="s">
+        <x:v>1064</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151" spans="1:14">
+      <x:c r="A151" s="0" t="s">
+        <x:v>1067</x:v>
+      </x:c>
+      <x:c r="B151" s="0" t="s">
+        <x:v>1068</x:v>
+      </x:c>
+      <x:c r="C151" s="0" t="s">
+        <x:v>1069</x:v>
+      </x:c>
+      <x:c r="D151" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E151" s="0" t="s">
+        <x:v>1070</x:v>
+      </x:c>
+      <x:c r="F151" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G151" s="0" t="s">
+        <x:v>1071</x:v>
+      </x:c>
+      <x:c r="H151" s="0" t="s">
+        <x:v>1072</x:v>
+      </x:c>
+      <x:c r="I151" s="0" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="N151" s="0" t="s">
+        <x:v>1064</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152" spans="1:14">
+      <x:c r="A152" s="0" t="s">
+        <x:v>1073</x:v>
+      </x:c>
+      <x:c r="B152" s="0" t="s">
+        <x:v>1074</x:v>
+      </x:c>
+      <x:c r="C152" s="0" t="s">
+        <x:v>1075</x:v>
+      </x:c>
+      <x:c r="D152" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E152" s="0" t="s">
+        <x:v>1076</x:v>
+      </x:c>
+      <x:c r="F152" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G152" s="0" t="s">
+        <x:v>1077</x:v>
+      </x:c>
+      <x:c r="H152" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="I152" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="N152" s="0" t="s">
+        <x:v>1078</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153" spans="1:14">
+      <x:c r="A153" s="0" t="s">
+        <x:v>1079</x:v>
+      </x:c>
+      <x:c r="B153" s="0" t="s">
+        <x:v>1080</x:v>
+      </x:c>
+      <x:c r="C153" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D153" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E153" s="0" t="s">
+        <x:v>1081</x:v>
+      </x:c>
+      <x:c r="F153" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G153" s="0" t="s">
+        <x:v>950</x:v>
+      </x:c>
+      <x:c r="H153" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="I153" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J153" s="0" t="s">
+        <x:v>1082</x:v>
+      </x:c>
+      <x:c r="K153" s="0" t="s">
+        <x:v>1083</x:v>
+      </x:c>
+      <x:c r="N153" s="0" t="s">
+        <x:v>1084</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
